--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/audit_trail_role_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/audit_trail_role_testcases.xlsx
@@ -244,7 +244,7 @@
       </c>
       <c r="L2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M2" t="inlineStr" s="2">
@@ -271,17 +271,17 @@
     <row r="3" ht="64" customHeight="1">
       <c r="A3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">新增</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="2">
@@ -357,17 +357,17 @@
     <row r="4" ht="64" customHeight="1">
       <c r="A4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">新增</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="2">
@@ -443,12 +443,12 @@
     <row r="5" ht="64" customHeight="1">
       <c r="A5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
@@ -505,7 +505,7 @@
       </c>
       <c r="L5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M5" t="inlineStr" s="2">
@@ -532,17 +532,17 @@
     <row r="6" ht="64" customHeight="1">
       <c r="A6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">编辑</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="2">
@@ -617,17 +617,17 @@
     <row r="7" ht="64" customHeight="1">
       <c r="A7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">编辑</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="2">
@@ -701,17 +701,17 @@
     <row r="8" ht="64" customHeight="1">
       <c r="A8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">编辑</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="2">
@@ -785,12 +785,12 @@
     <row r="9" ht="64" customHeight="1">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
@@ -844,7 +844,7 @@
       </c>
       <c r="L9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M9" t="inlineStr" s="2">
@@ -871,17 +871,17 @@
     <row r="10" ht="64" customHeight="1">
       <c r="A10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">删除</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="2">
@@ -958,17 +958,17 @@
     <row r="11" ht="64" customHeight="1">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">删除</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="2">
@@ -1042,12 +1042,12 @@
     <row r="12" ht="64" customHeight="1">
       <c r="A12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
@@ -1128,17 +1128,17 @@
     <row r="13" ht="64" customHeight="1">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">批量删除</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="2">
@@ -1213,17 +1213,17 @@
     <row r="14" ht="64" customHeight="1">
       <c r="A14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">批量删除</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="2">
@@ -1297,12 +1297,12 @@
     <row r="15" ht="64" customHeight="1">
       <c r="A15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M15" t="inlineStr" s="2">
@@ -1383,17 +1383,17 @@
     <row r="16" ht="64" customHeight="1">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="2">
@@ -1470,17 +1470,17 @@
     <row r="17" ht="64" customHeight="1">
       <c r="A17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="2">
@@ -1554,17 +1554,17 @@
     <row r="18" ht="64" customHeight="1">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="2">
@@ -1638,12 +1638,12 @@
     <row r="19" ht="64" customHeight="1">
       <c r="A19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="L19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M19" t="inlineStr" s="2">
@@ -1724,17 +1724,17 @@
     <row r="20" ht="64" customHeight="1">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">启用</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="2">
@@ -1809,17 +1809,17 @@
     <row r="21" ht="64" customHeight="1">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">启用</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="2">
@@ -1893,12 +1893,12 @@
     <row r="22" ht="64" customHeight="1">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="L22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M22" t="inlineStr" s="2">
@@ -1979,17 +1979,17 @@
     <row r="23" ht="64" customHeight="1">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">停用</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="2">
@@ -2064,17 +2064,17 @@
     <row r="24" ht="64" customHeight="1">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">停用</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="2">
@@ -2148,12 +2148,12 @@
     <row r="25" ht="64" customHeight="1">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
@@ -2234,17 +2234,17 @@
     <row r="26" ht="64" customHeight="1">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="2">
@@ -2320,17 +2320,17 @@
     <row r="27" ht="64" customHeight="1">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="2">
@@ -2404,12 +2404,12 @@
     <row r="28" ht="64" customHeight="1">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="L28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M28" t="inlineStr" s="2">
@@ -2490,17 +2490,17 @@
     <row r="29" ht="64" customHeight="1">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="2">
@@ -2576,17 +2576,17 @@
     <row r="30" ht="64" customHeight="1">
       <c r="A30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="2">
@@ -2660,12 +2660,12 @@
     <row r="31" ht="64" customHeight="1">
       <c r="A31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
@@ -2744,17 +2744,17 @@
     <row r="32" ht="64" customHeight="1">
       <c r="A32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">搜索</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="2">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="L32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M32" t="inlineStr" s="2">
@@ -2829,17 +2829,17 @@
     <row r="33" ht="64" customHeight="1">
       <c r="A33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">搜索</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="2">

--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/audit_trail_role_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/audit_trail_role_testcases.xlsx
@@ -77,7 +77,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:P34"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -217,24 +217,21 @@
       </c>
       <c r="H2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色管理新增权限和审计追踪查看权限</t>
+          <t xml:space="preserve">普通用户已登录业务站点 A，所属启用角色拥有角色管理菜单权限、角色新增按钮权限和审计追踪菜单权限</t>
         </is>
       </c>
       <c r="I2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入业务站点 - 角色管理模块
-2. 新增角色成功
+          <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
+2. 新增角色 R 并保存成功
 3. 进入审计追踪模块查看列表</t>
         </is>
       </c>
       <c r="J2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">列表新增一条记录显示在第一行，数据正确：
-1. 操作人：当前登录用户姓名
-2. 操作时间：格式 yyyy-mm-dd hh:mm:ss
-3. 所属模块：角色管理
-4. 操作类型：新增
-5. 受影响对象：新增的角色名称</t>
+          <t xml:space="preserve">1. 审计追踪列表第一行新增角色管理记录
+2. 操作人为当前用户姓名；操作时间格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理
+3. 操作类型为新增；受影响对象为新增的角色名称</t>
         </is>
       </c>
       <c r="K2" t="inlineStr" s="2">
@@ -244,7 +241,7 @@
       </c>
       <c r="L2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M2" t="inlineStr" s="2">
@@ -286,12 +283,12 @@
       </c>
       <c r="D3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">查看新增角色的审计追踪详情，验证数据正确</t>
+          <t xml:space="preserve">查看新增角色审计追踪详情，验证数据正确</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="2">
@@ -306,21 +303,22 @@
       </c>
       <c r="H3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色管理新增权限和审计追踪查看权限</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理新增按钮权限和审计追踪菜单权限
+2. 系统已存在新增成功的角色 R，角色名称、角色编号和状态均有明确值</t>
         </is>
       </c>
       <c r="I3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入业务站点 - 角色管理模块
-2. 新增角色成功
-3. 进入审计追踪模块，点击对应记录的受影响对象</t>
+          <t xml:space="preserve">1. 进入审计追踪模块
+2. 按所属模块角色管理、操作类型新增筛选记录
+3. 点击新增记录的受影响对象查看详情</t>
         </is>
       </c>
       <c r="J3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 审计追踪详情弹窗，分为基本信息和内容详情两部分
-2. 基本信息：操作人、操作时间、操作模块（角色管理）、操作类型（新增）显示正确
-3. 内容详情：角色名称、角色编号、状态与实际新增内容一致</t>
+          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
+2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为新增
+3. 内容详情显示角色名称、角色编号、状态，且与新增角色 R 一致</t>
         </is>
       </c>
       <c r="K3" t="inlineStr" s="2">
@@ -372,7 +370,7 @@
       </c>
       <c r="D4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出新增角色的审计追踪详情，验证导出内容一致</t>
+          <t xml:space="preserve">导出新增角色审计追踪详情，验证导出内容一致</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -392,21 +390,22 @@
       </c>
       <c r="H4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色管理新增权限和审计追踪导出权限</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限
+2. 审计追踪列表存在角色管理新增记录</t>
         </is>
       </c>
       <c r="I4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入业务站点 - 角色管理模块
-2. 新增角色成功
-3. 进入审计追踪，点击对应记录受影响对象
-4. 点击详情页导出按钮</t>
+          <t xml:space="preserve">1. 进入审计追踪模块
+2. 点击新增记录的受影响对象查看详情
+3. 点击详情页导出按钮
+4. 打开下载的 PDF 文件</t>
         </is>
       </c>
       <c r="J4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 下载 pdf 文件到本地，文件名：&lt;受影响对象&gt;.pdf
-2. 导出内容与页面详情展示一致</t>
+          <t xml:space="preserve">1. 下载 PDF 文件到本地，文件名为&lt;受影响对象&gt;.pdf
+2. PDF 中基本信息和内容详情与页面详情展示一致</t>
         </is>
       </c>
       <c r="K4" t="inlineStr" s="2">
@@ -458,12 +457,12 @@
       </c>
       <c r="D5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">编辑角色成功，审计追踪列表新增对应记录</t>
+          <t xml:space="preserve">查看编辑角色审计追踪详情，验证新旧值对比正确</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr" s="2">
@@ -478,34 +477,33 @@
       </c>
       <c r="H5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色管理编辑权限和审计追踪查看权限
-2. 业务站点已存在可编辑角色</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理编辑按钮权限和审计追踪菜单权限
+2. 系统已存在可编辑角色 R，且已记录修改前角色名称</t>
         </is>
       </c>
       <c r="I5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理，编辑角色名称后保存
-2. 进入审计追踪模块查看列表</t>
+          <t xml:space="preserve">1. 进入角色管理列表页
+2. 修改角色 R 的角色名称并保存成功
+3. 进入审计追踪模块，点击编辑记录的受影响对象查看详情</t>
         </is>
       </c>
       <c r="J5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">列表新增一条记录显示在第一行，数据正确：
-1. 操作人：当前登录用户姓名
-2. 操作时间：格式 yyyy-mm-dd hh:mm:ss
-3. 所属模块：角色管理
-4. 操作类型：编辑
-5. 受影响对象：编辑的角色名称</t>
+          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
+2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为编辑
+3. 内容详情显示角色编号，且角色编号不可修改但可定位被修改角色
+4. 内容详情显示角色名称修改前值和修改后值对比</t>
         </is>
       </c>
       <c r="K5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、priority_rules.md-P0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M5" t="inlineStr" s="2">
@@ -547,12 +545,12 @@
       </c>
       <c r="D6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">查看编辑角色的审计追踪详情，验证角色名称新旧值对比正确</t>
+          <t xml:space="preserve">编辑角色成功，审计追踪列表新增对应记录</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="2">
@@ -567,20 +565,22 @@
       </c>
       <c r="H6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色管理编辑权限和审计追踪查看权限
-2. 业务站点已存在可编辑角色</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理菜单权限、角色编辑按钮权限和审计追踪菜单权限
+2. 系统已存在可编辑角色 R</t>
         </is>
       </c>
       <c r="I6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理，修改角色名称后保存（记录修改前后值）
-2. 进入审计追踪，点击对应记录受影响对象</t>
+          <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
+2. 编辑角色 R 的角色名称并保存成功
+3. 进入审计追踪模块查看列表</t>
         </is>
       </c>
       <c r="J6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 详情弹窗基本信息：操作人、操作时间、操作模块（角色管理）、操作类型（编辑）显示正确
-2. 内容详情：角色编号显示（不允许修改但记录被修改的角色）、角色名称显示修改前后新旧值对比</t>
+          <t xml:space="preserve">1. 审计追踪列表第一行新增角色管理记录
+2. 操作人为当前用户姓名；操作时间格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理
+3. 操作类型为编辑；受影响对象为编辑后的角色名称</t>
         </is>
       </c>
       <c r="K6" t="inlineStr" s="2">
@@ -632,7 +632,7 @@
       </c>
       <c r="D7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">进入编辑页不修改直接保存，审计追踪不新增记录</t>
+          <t xml:space="preserve">编辑角色无实际变更，审计追踪不新增记录</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -652,24 +652,24 @@
       </c>
       <c r="H7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色管理编辑权限和审计追踪查看权限
-2. 业务站点已存在可编辑角色</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理编辑按钮权限和审计追踪菜单权限
+2. 系统已存在可编辑角色 R</t>
         </is>
       </c>
       <c r="I7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理，进入编辑页不修改任何内容直接保存
-2. 进入审计追踪模块查看列表</t>
+          <t xml:space="preserve">1. 进入角色管理编辑页，不修改任何字段直接保存或取消
+2. 进入审计追踪模块查看角色管理记录</t>
         </is>
       </c>
       <c r="J7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪模块不新增对应记录</t>
+          <t xml:space="preserve">审计追踪模块不新增角色管理编辑记录</t>
         </is>
       </c>
       <c r="K7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L7" t="inlineStr" s="2">
@@ -716,7 +716,7 @@
       </c>
       <c r="D8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出编辑角色的审计追踪详情，验证导出内容一致</t>
+          <t xml:space="preserve">导出编辑角色审计追踪详情，验证导出内容一致</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -736,19 +736,22 @@
       </c>
       <c r="H8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色管理编辑权限和审计追踪导出权限</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限
+2. 审计追踪列表存在角色管理编辑记录</t>
         </is>
       </c>
       <c r="I8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 编辑角色成功后，进入审计追踪点击对应记录受影响对象
-2. 点击详情页导出按钮</t>
+          <t xml:space="preserve">1. 进入审计追踪模块
+2. 点击编辑记录的受影响对象查看详情
+3. 点击详情页导出按钮
+4. 打开下载的 PDF 文件</t>
         </is>
       </c>
       <c r="J8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 下载 pdf 文件到本地，文件名：&lt;受影响对象&gt;.pdf
-2. 导出内容与页面详情展示一致</t>
+          <t xml:space="preserve">1. 下载 PDF 文件到本地，文件名为&lt;受影响对象&gt;.pdf
+2. PDF 中基本信息、角色编号和角色名称新旧值对比与页面详情展示一致</t>
         </is>
       </c>
       <c r="K8" t="inlineStr" s="2">
@@ -800,12 +803,12 @@
       </c>
       <c r="D9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">删除角色成功，审计追踪列表新增对应记录</t>
+          <t xml:space="preserve">查看删除角色审计追踪详情，验证权限和用户信息完整</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="2">
@@ -820,31 +823,34 @@
       </c>
       <c r="H9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色管理删除权限和审计追踪查看权限
-2. 业务站点已存在配置了权限和用户的角色</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理删除按钮权限和审计追踪菜单权限
+2. 系统已存在配置了功能权限、产品数据权限和分配用户的角色 R</t>
         </is>
       </c>
       <c r="I9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理，删除角色成功
-2. 进入审计追踪模块查看列表</t>
+          <t xml:space="preserve">1. 进入角色管理列表页
+2. 删除角色 R 并确认成功
+3. 进入审计追踪模块，点击删除记录的受影响对象查看详情</t>
         </is>
       </c>
       <c r="J9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">列表新增一条记录，数据正确：
-1. 操作人、操作时间（yyyy-mm-dd hh:mm:ss）、所属模块（角色管理）、操作类型（删除）
-2. 受影响对象：已删除的角色名称</t>
+          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
+2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为删除
+3. 内容详情显示角色名称、角色编号、状态
+4. 功能权限详情显示格式为菜单权限（按钮权限1、按钮权限2），多个菜单权限用顿号隔开
+5. 产品数据权限详情显示数据权限、已选产品，多个产品用顿号隔开；分配用户详情显示用户部门、姓名、编号</t>
         </is>
       </c>
       <c r="K9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、priority_rules.md-P0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M9" t="inlineStr" s="2">
@@ -886,12 +892,12 @@
       </c>
       <c r="D10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">查看删除角色的审计追踪详情，验证权限和用户信息完整</t>
+          <t xml:space="preserve">删除角色成功，审计追踪列表新增对应记录</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="2">
@@ -906,22 +912,22 @@
       </c>
       <c r="H10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色管理删除权限和审计追踪查看权限
-2. 已删除一个配置了功能权限、产品数据权限和分配用户的角色</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理菜单权限、角色删除按钮权限和审计追踪菜单权限
+2. 系统已存在可删除角色 R</t>
         </is>
       </c>
       <c r="I10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入审计追踪，点击对应删除记录受影响对象</t>
+          <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
+2. 删除角色 R 并确认成功
+3. 进入审计追踪模块查看列表</t>
         </is>
       </c>
       <c r="J10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 详情弹窗基本信息：操作人、操作时间、操作模块（角色管理）、操作类型（删除）显示正确
-2. 内容详情：角色名称、角色编号、状态
-3. 功能权限详情：菜单权限（按钮权限）格式正确，多个按钮用顿号隔开
-4. 产品数据权限详情：数据权限类型、已选产品（多个顿号隔开）
-5. 分配用户详情：用户部门、姓名、编号</t>
+          <t xml:space="preserve">1. 审计追踪列表第一行新增角色管理记录
+2. 操作人为当前用户姓名；操作时间格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理
+3. 操作类型为删除；受影响对象为已删除的角色名称</t>
         </is>
       </c>
       <c r="K10" t="inlineStr" s="2">
@@ -973,7 +979,7 @@
       </c>
       <c r="D11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出删除角色的审计追踪详情，验证导出内容一致</t>
+          <t xml:space="preserve">导出删除角色审计追踪详情，验证导出内容一致</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -993,19 +999,22 @@
       </c>
       <c r="H11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色管理删除权限和审计追踪导出权限</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限
+2. 审计追踪列表存在角色管理删除记录</t>
         </is>
       </c>
       <c r="I11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 删除角色成功后，进入审计追踪点击对应记录受影响对象
-2. 点击详情页导出按钮</t>
+          <t xml:space="preserve">1. 进入审计追踪模块
+2. 点击删除记录的受影响对象查看详情
+3. 点击详情页导出按钮
+4. 打开下载的 PDF 文件</t>
         </is>
       </c>
       <c r="J11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 下载 pdf 文件到本地，文件名：&lt;受影响对象&gt;.pdf
-2. 导出内容与页面详情展示一致</t>
+          <t xml:space="preserve">1. 下载 PDF 文件到本地，文件名为&lt;受影响对象&gt;.pdf
+2. PDF 中基本信息、角色信息、功能权限详情、产品数据权限详情和分配用户详情与页面详情展示一致</t>
         </is>
       </c>
       <c r="K11" t="inlineStr" s="2">
@@ -1057,12 +1066,12 @@
       </c>
       <c r="D12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">批量删除角色成功，审计追踪列表新增对应记录</t>
+          <t xml:space="preserve">查看批量删除角色审计追踪详情，验证删除数量和明细完整</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="2">
@@ -1077,31 +1086,34 @@
       </c>
       <c r="H12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色管理批量删除权限和审计追踪查看权限
-2. 业务站点已存在多个角色</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有批量删除按钮权限和审计追踪菜单权限
+2. 系统已存在多个配置了功能权限、产品数据权限和分配用户的可删除角色</t>
         </is>
       </c>
       <c r="I12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理，勾选多个角色批量删除成功
-2. 进入审计追踪模块查看列表</t>
+          <t xml:space="preserve">1. 进入角色管理列表页
+2. 勾选多个角色并批量删除成功
+3. 进入审计追踪模块，点击批量删除记录的受影响对象查看详情</t>
         </is>
       </c>
       <c r="J12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">列表新增一条记录，数据正确：
-1. 操作人、操作时间（yyyy-mm-dd hh:mm:ss）、所属模块（角色管理）、操作类型（批量删除）
-2. 受影响对象格式：角色管理_批量删除_xx项（xx 为实际删除数量）</t>
+          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
+2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为批量删除
+3. 内容详情显示删除数量，且与实际批量删除角色数量一致
+4. 删除详情逐条显示角色名称、角色编号、状态、功能权限详情、产品数据权限详情、分配用户详情
+5. 功能权限详情格式为菜单权限（按钮权限1、按钮权限2），已选产品多个值用顿号隔开</t>
         </is>
       </c>
       <c r="K12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、priority_rules.md-P0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M12" t="inlineStr" s="2">
@@ -1143,12 +1155,12 @@
       </c>
       <c r="D13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">查看批量删除角色的审计追踪详情，验证删除数量及每个角色完整信息</t>
+          <t xml:space="preserve">批量删除角色成功，审计追踪列表新增对应记录</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="2">
@@ -1163,20 +1175,22 @@
       </c>
       <c r="H13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色管理批量删除权限和审计追踪查看权限
-2. 已批量删除多个配置了权限和用户的角色</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理菜单权限、批量删除按钮权限和审计追踪菜单权限
+2. 系统已存在多个可删除角色</t>
         </is>
       </c>
       <c r="I13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入审计追踪，点击批量删除记录受影响对象</t>
+          <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
+2. 勾选多个角色并批量删除成功
+3. 进入审计追踪模块查看列表</t>
         </is>
       </c>
       <c r="J13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 详情弹窗基本信息：操作人、操作时间、操作模块（角色管理）、操作类型（批量删除）显示正确
-2. 内容详情：删除数量与实际一致
-3. 删除详情列出每个角色：角色名称、角色编号、状态、功能权限详情（菜单权限（按钮权限），多按钮顿号隔开）、产品数据权限详情（已选产品（多个顿号隔开））、分配用户详情（用户部门、姓名、编号）</t>
+          <t xml:space="preserve">1. 审计追踪列表第一行新增角色管理记录
+2. 操作人为当前用户姓名；操作时间格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理
+3. 操作类型为批量删除；受影响对象为角色管理批量删除记录</t>
         </is>
       </c>
       <c r="K13" t="inlineStr" s="2">
@@ -1228,7 +1242,7 @@
       </c>
       <c r="D14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出批量删除角色的审计追踪详情，验证导出内容一致</t>
+          <t xml:space="preserve">导出批量删除角色审计追踪详情，验证导出内容一致</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -1248,19 +1262,22 @@
       </c>
       <c r="H14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色管理批量删除权限和审计追踪导出权限</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限
+2. 审计追踪列表存在角色管理批量删除记录</t>
         </is>
       </c>
       <c r="I14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 批量删除角色成功后，进入审计追踪点击对应记录受影响对象
-2. 点击详情页导出按钮</t>
+          <t xml:space="preserve">1. 进入审计追踪模块
+2. 点击批量删除记录的受影响对象查看详情
+3. 点击详情页导出按钮
+4. 打开下载的 PDF 文件</t>
         </is>
       </c>
       <c r="J14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 下载 pdf 文件到本地，文件名：&lt;受影响对象&gt;.pdf
-2. 导出内容与页面详情展示一致，包含删除数量和每个角色完整信息</t>
+          <t xml:space="preserve">1. 下载 PDF 文件到本地，文件名为&lt;受影响对象&gt;.pdf
+2. PDF 中删除数量和每条删除详情与页面详情展示一致</t>
         </is>
       </c>
       <c r="K14" t="inlineStr" s="2">
@@ -1312,12 +1329,12 @@
       </c>
       <c r="D15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置角色权限成功，审计追踪列表新增对应记录</t>
+          <t xml:space="preserve">查看配置角色审计追踪详情，验证权限和用户信息完整</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="2">
@@ -1332,31 +1349,34 @@
       </c>
       <c r="H15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色配置权限和审计追踪查看权限
-2. 业务站点已存在可配置角色</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色配置按钮权限和审计追踪菜单权限
+2. 系统已存在已配置功能权限、产品数据权限和分配用户的角色 R</t>
         </is>
       </c>
       <c r="I15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理，配置功能权限、产品数据权限、分配用户后保存
-2. 进入审计追踪模块查看列表</t>
+          <t xml:space="preserve">1. 进入角色管理配置页
+2. 配置角色 R 的功能权限、产品数据权限和分配用户并保存成功
+3. 进入审计追踪模块，点击配置记录的受影响对象查看详情</t>
         </is>
       </c>
       <c r="J15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">列表新增一条记录，数据正确：
-1. 操作人、操作时间（yyyy-mm-dd hh:mm:ss）、所属模块（角色管理）、操作类型（配置）
-2. 受影响对象：配置的角色名称</t>
+          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
+2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为配置
+3. 内容详情显示角色名称、角色编号、状态
+4. 功能权限详情显示格式为菜单权限（按钮权限1、按钮权限2），多个菜单权限用顿号隔开
+5. 产品数据权限详情显示数据权限、已选产品，多个产品用顿号隔开；分配用户详情显示用户部门、姓名、编号</t>
         </is>
       </c>
       <c r="K15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、priority_rules.md-P0</t>
         </is>
       </c>
       <c r="L15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M15" t="inlineStr" s="2">
@@ -1398,12 +1418,12 @@
       </c>
       <c r="D16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">查看配置角色的审计追踪详情，验证权限和用户信息完整</t>
+          <t xml:space="preserve">配置角色权限成功，审计追踪列表新增对应记录</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="2">
@@ -1418,22 +1438,22 @@
       </c>
       <c r="H16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色配置权限和审计追踪查看权限
-2. 已配置一个角色的功能权限、产品数据权限和分配用户</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理菜单权限、角色配置按钮权限和审计追踪菜单权限
+2. 系统已存在可配置角色 R</t>
         </is>
       </c>
       <c r="I16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入审计追踪，点击对应配置记录受影响对象</t>
+          <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
+2. 配置角色 R 的功能权限、产品数据权限和分配用户并保存成功
+3. 进入审计追踪模块查看列表</t>
         </is>
       </c>
       <c r="J16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 详情弹窗基本信息：操作人、操作时间、操作模块（角色管理）、操作类型（配置）显示正确
-2. 内容详情：角色名称、角色编号、状态
-3. 功能权限详情：菜单权限（按钮权限）格式正确，多按钮顿号隔开
-4. 产品数据权限详情：数据权限类型、已选产品（多个顿号隔开）
-5. 分配用户详情：用户部门、姓名、编号</t>
+          <t xml:space="preserve">1. 审计追踪列表第一行新增角色管理记录
+2. 操作人为当前用户姓名；操作时间格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理
+3. 操作类型为配置；受影响对象为配置的角色名称</t>
         </is>
       </c>
       <c r="K16" t="inlineStr" s="2">
@@ -1485,7 +1505,7 @@
       </c>
       <c r="D17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">进入配置页不修改直接保存，审计追踪不新增记录</t>
+          <t xml:space="preserve">配置角色无实际变更，审计追踪不新增记录</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -1505,24 +1525,24 @@
       </c>
       <c r="H17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色配置权限和审计追踪查看权限
-2. 业务站点已存在可配置角色</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色配置按钮权限和审计追踪菜单权限
+2. 系统已存在可配置角色 R</t>
         </is>
       </c>
       <c r="I17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理，进入配置页不修改任何内容直接保存
-2. 进入审计追踪模块查看列表</t>
+          <t xml:space="preserve">1. 进入角色管理配置页，不修改功能权限、产品数据权限或分配用户直接保存或取消
+2. 进入审计追踪模块查看角色管理记录</t>
         </is>
       </c>
       <c r="J17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪模块不新增对应记录</t>
+          <t xml:space="preserve">审计追踪模块不新增角色管理配置记录</t>
         </is>
       </c>
       <c r="K17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L17" t="inlineStr" s="2">
@@ -1569,7 +1589,7 @@
       </c>
       <c r="D18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出配置角色的审计追踪详情，验证导出内容一致</t>
+          <t xml:space="preserve">导出配置角色审计追踪详情，验证导出内容一致</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -1589,19 +1609,22 @@
       </c>
       <c r="H18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色配置权限和审计追踪导出权限</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限
+2. 审计追踪列表存在角色管理配置记录</t>
         </is>
       </c>
       <c r="I18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 配置角色成功后，进入审计追踪点击对应记录受影响对象
-2. 点击详情页导出按钮</t>
+          <t xml:space="preserve">1. 进入审计追踪模块
+2. 点击配置记录的受影响对象查看详情
+3. 点击详情页导出按钮
+4. 打开下载的 PDF 文件</t>
         </is>
       </c>
       <c r="J18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 下载 pdf 文件到本地，文件名：&lt;受影响对象&gt;.pdf
-2. 导出内容与页面详情展示一致</t>
+          <t xml:space="preserve">1. 下载 PDF 文件到本地，文件名为&lt;受影响对象&gt;.pdf
+2. PDF 中角色信息、功能权限详情、产品数据权限详情和分配用户详情与页面详情展示一致</t>
         </is>
       </c>
       <c r="K18" t="inlineStr" s="2">
@@ -1673,21 +1696,22 @@
       </c>
       <c r="H19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色启用权限和审计追踪查看权限
-2. 已存在停用状态角色</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理菜单权限、角色启用按钮权限和审计追踪菜单权限
+2. 系统已存在停用状态角色 R</t>
         </is>
       </c>
       <c r="I19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理，启用角色成功
-2. 进入审计追踪模块查看列表</t>
+          <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
+2. 启用角色 R 成功
+3. 进入审计追踪模块查看列表</t>
         </is>
       </c>
       <c r="J19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">列表新增一条记录，数据正确：
-1. 操作人、操作时间（yyyy-mm-dd hh:mm:ss）、所属模块（角色管理）、操作类型（启用）
-2. 受影响对象：启用的角色名称</t>
+          <t xml:space="preserve">1. 审计追踪列表第一行新增角色管理记录
+2. 操作人为当前用户姓名；操作时间格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理
+3. 操作类型为启用；受影响对象为启用的角色名称</t>
         </is>
       </c>
       <c r="K19" t="inlineStr" s="2">
@@ -1739,12 +1763,12 @@
       </c>
       <c r="D20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">查看启用角色的审计追踪详情，验证数据正确</t>
+          <t xml:space="preserve">查看启用角色审计追踪详情，验证状态正确</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="2">
@@ -1759,20 +1783,22 @@
       </c>
       <c r="H20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色启用权限和审计追踪查看权限
-2. 已存在停用状态角色</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色启用按钮权限和审计追踪菜单权限
+2. 系统已存在已启用成功的角色 R</t>
         </is>
       </c>
       <c r="I20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 启用角色成功
-2. 进入审计追踪，点击对应记录受影响对象</t>
+          <t xml:space="preserve">1. 进入审计追踪模块
+2. 按所属模块角色管理、操作类型启用筛选记录
+3. 点击启用记录的受影响对象查看详情</t>
         </is>
       </c>
       <c r="J20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 详情弹窗基本信息：操作人、操作时间、操作模块（角色管理）、操作类型（启用）显示正确
-2. 内容详情：角色名称、角色编号、状态（显示启用后状态）显示正确</t>
+          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
+2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为启用
+3. 内容详情显示角色名称、角色编号、状态，状态与启用后的角色状态一致</t>
         </is>
       </c>
       <c r="K20" t="inlineStr" s="2">
@@ -1824,7 +1850,7 @@
       </c>
       <c r="D21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出启用角色的审计追踪详情，验证导出内容一致</t>
+          <t xml:space="preserve">导出启用角色审计追踪详情，验证导出内容一致</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -1844,19 +1870,22 @@
       </c>
       <c r="H21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色启用权限和审计追踪导出权限</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限
+2. 审计追踪列表存在角色管理启用记录</t>
         </is>
       </c>
       <c r="I21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 启用角色成功后，进入审计追踪点击对应记录受影响对象
-2. 点击详情页导出按钮</t>
+          <t xml:space="preserve">1. 进入审计追踪模块
+2. 点击启用记录的受影响对象查看详情
+3. 点击详情页导出按钮
+4. 打开下载的 PDF 文件</t>
         </is>
       </c>
       <c r="J21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 下载 pdf 文件到本地，文件名：&lt;受影响对象&gt;.pdf
-2. 导出内容与页面详情展示一致</t>
+          <t xml:space="preserve">1. 下载 PDF 文件到本地，文件名为&lt;受影响对象&gt;.pdf
+2. PDF 中基本信息、角色名称、角色编号和状态与页面详情展示一致</t>
         </is>
       </c>
       <c r="K21" t="inlineStr" s="2">
@@ -1928,21 +1957,22 @@
       </c>
       <c r="H22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色停用权限和审计追踪查看权限
-2. 已存在启用状态角色</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理菜单权限、角色停用按钮权限和审计追踪菜单权限
+2. 系统已存在启用状态角色 R</t>
         </is>
       </c>
       <c r="I22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理，停用角色成功
-2. 进入审计追踪模块查看列表</t>
+          <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
+2. 停用角色 R 成功
+3. 进入审计追踪模块查看列表</t>
         </is>
       </c>
       <c r="J22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">列表新增一条记录，数据正确：
-1. 操作人、操作时间（yyyy-mm-dd hh:mm:ss）、所属模块（角色管理）、操作类型（停用）
-2. 受影响对象：停用的角色名称</t>
+          <t xml:space="preserve">1. 审计追踪列表第一行新增角色管理记录
+2. 操作人为当前用户姓名；操作时间格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理
+3. 操作类型为停用；受影响对象为停用的角色名称</t>
         </is>
       </c>
       <c r="K22" t="inlineStr" s="2">
@@ -1994,12 +2024,12 @@
       </c>
       <c r="D23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">查看停用角色的审计追踪详情，验证数据正确</t>
+          <t xml:space="preserve">查看停用角色审计追踪详情，验证状态正确</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="2">
@@ -2014,20 +2044,22 @@
       </c>
       <c r="H23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色停用权限和审计追踪查看权限
-2. 已存在启用状态角色</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色停用按钮权限和审计追踪菜单权限
+2. 系统已存在已停用成功的角色 R</t>
         </is>
       </c>
       <c r="I23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 停用角色成功
-2. 进入审计追踪，点击对应记录受影响对象</t>
+          <t xml:space="preserve">1. 进入审计追踪模块
+2. 按所属模块角色管理、操作类型停用筛选记录
+3. 点击停用记录的受影响对象查看详情</t>
         </is>
       </c>
       <c r="J23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 详情弹窗基本信息：操作人、操作时间、操作模块（角色管理）、操作类型（停用）显示正确
-2. 内容详情：角色名称、角色编号、状态（显示停用后状态）显示正确</t>
+          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
+2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为停用
+3. 内容详情显示角色名称、角色编号、状态，状态与停用后的角色状态一致</t>
         </is>
       </c>
       <c r="K23" t="inlineStr" s="2">
@@ -2079,7 +2111,7 @@
       </c>
       <c r="D24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出停用角色的审计追踪详情，验证导出内容一致</t>
+          <t xml:space="preserve">导出停用角色审计追踪详情，验证导出内容一致</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -2099,19 +2131,22 @@
       </c>
       <c r="H24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色停用权限和审计追踪导出权限</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限
+2. 审计追踪列表存在角色管理停用记录</t>
         </is>
       </c>
       <c r="I24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 停用角色成功后，进入审计追踪点击对应记录受影响对象
-2. 点击详情页导出按钮</t>
+          <t xml:space="preserve">1. 进入审计追踪模块
+2. 点击停用记录的受影响对象查看详情
+3. 点击详情页导出按钮
+4. 打开下载的 PDF 文件</t>
         </is>
       </c>
       <c r="J24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 下载 pdf 文件到本地，文件名：&lt;受影响对象&gt;.pdf
-2. 导出内容与页面详情展示一致</t>
+          <t xml:space="preserve">1. 下载 PDF 文件到本地，文件名为&lt;受影响对象&gt;.pdf
+2. PDF 中基本信息、角色名称、角色编号和状态与页面详情展示一致</t>
         </is>
       </c>
       <c r="K24" t="inlineStr" s="2">
@@ -2163,12 +2198,12 @@
       </c>
       <c r="D25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入角色成功，审计追踪列表新增对应记录</t>
+          <t xml:space="preserve">查看导入角色审计追踪详情，验证文件名、数量和数据列表正确</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="2">
@@ -2183,26 +2218,29 @@
       </c>
       <c r="H25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色导入权限和审计追踪查看权限
-2. 已准备合法格式的角色导入文件</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色导入按钮权限和审计追踪菜单权限
+2. 系统已成功导入包含多条角色数据的 Excel 文件</t>
         </is>
       </c>
       <c r="I25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理，导入角色文件成功
-2. 进入审计追踪模块查看列表</t>
+          <t xml:space="preserve">1. 进入审计追踪模块
+2. 按所属模块角色管理、操作类型导入筛选记录
+3. 点击导入记录的受影响对象查看详情</t>
         </is>
       </c>
       <c r="J25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">列表新增一条记录，数据正确：
-1. 操作人、操作时间（yyyy-mm-dd hh:mm:ss）、所属模块（角色管理）、操作类型（导入）
-2. 受影响对象：导入的文件名或对应标识</t>
+          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
+2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为导入
+3. 内容详情显示导入文件名、导入数量，且与实际导入文件一致
+4. 导入数据列表中每条数据包含角色名称、角色编号、状态、菜单权限、按钮权限、分配用户、数据权限、已选产品
+5. 按钮权限记录格式为菜单权限1（按钮1、按钮2）、菜单权限2（按钮3、按钮4）</t>
         </is>
       </c>
       <c r="K25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、priority_rules.md-P0</t>
         </is>
       </c>
       <c r="L25" t="inlineStr" s="2">
@@ -2249,12 +2287,12 @@
       </c>
       <c r="D26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">查看导入角色的审计追踪详情，验证文件名、数量及数据列表正确</t>
+          <t xml:space="preserve">导入角色成功，审计追踪列表新增对应记录</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="2">
@@ -2269,21 +2307,22 @@
       </c>
       <c r="H26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色导入权限和审计追踪查看权限
-2. 已成功导入含多条角色数据的文件</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理菜单权限、角色导入按钮权限和审计追踪菜单权限
+2. 已准备合法的角色导入 Excel 文件</t>
         </is>
       </c>
       <c r="I26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入审计追踪，点击导入记录受影响对象</t>
+          <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
+2. 导入角色文件成功
+3. 进入审计追踪模块查看列表</t>
         </is>
       </c>
       <c r="J26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 详情弹窗基本信息：操作人、操作时间、操作模块（角色管理）、操作类型（导入）显示正确
-2. 内容详情：导入文件名与实际文件名一致、导入数量与实际条数一致
-3. 导入数据列表：每条角色包含角色名称、角色编号、状态、菜单权限、按钮权限、分配用户、数据权限、已选产品
-4. 按钮权限格式：菜单权限1（按钮1、按钮2）、菜单权限2（按钮3、按钮4）</t>
+          <t xml:space="preserve">1. 审计追踪列表第一行新增角色管理记录
+2. 操作人为当前用户姓名；操作时间格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理
+3. 操作类型为导入；受影响对象为导入文件名</t>
         </is>
       </c>
       <c r="K26" t="inlineStr" s="2">
@@ -2335,7 +2374,7 @@
       </c>
       <c r="D27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出导入角色的审计追踪详情，验证导出内容一致</t>
+          <t xml:space="preserve">导出导入角色审计追踪详情，验证导出内容一致</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -2355,19 +2394,22 @@
       </c>
       <c r="H27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色导入权限和审计追踪导出权限</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限
+2. 审计追踪列表存在角色管理导入记录</t>
         </is>
       </c>
       <c r="I27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 导入角色成功后，进入审计追踪点击对应记录受影响对象
-2. 点击详情页导出按钮</t>
+          <t xml:space="preserve">1. 进入审计追踪模块
+2. 点击导入记录的受影响对象查看详情
+3. 点击详情页导出按钮
+4. 打开下载的 PDF 文件</t>
         </is>
       </c>
       <c r="J27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 下载 pdf 文件到本地，文件名：&lt;受影响对象&gt;.pdf
-2. 导出内容与页面详情展示一致，包含文件名、导入数量和数据列表</t>
+          <t xml:space="preserve">1. 下载 PDF 文件到本地，文件名为&lt;受影响对象&gt;.pdf
+2. PDF 中导入文件名、导入数量和导入数据列表与页面详情展示一致</t>
         </is>
       </c>
       <c r="K27" t="inlineStr" s="2">
@@ -2419,12 +2461,12 @@
       </c>
       <c r="D28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出角色成功，审计追踪列表新增对应记录</t>
+          <t xml:space="preserve">查看导出角色审计追踪详情，验证数量、环境和数据列表正确</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="2">
@@ -2439,31 +2481,34 @@
       </c>
       <c r="H28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色导出权限和审计追踪查看权限
-2. 角色管理列表已有数据</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色导出按钮权限和审计追踪菜单权限
+2. 系统已成功导出多条角色数据</t>
         </is>
       </c>
       <c r="I28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理，导出角色成功
-2. 进入审计追踪模块查看列表</t>
+          <t xml:space="preserve">1. 进入审计追踪模块
+2. 按所属模块角色管理、操作类型导出筛选记录
+3. 点击导出记录的受影响对象查看详情</t>
         </is>
       </c>
       <c r="J28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">列表新增一条记录，数据正确：
-1. 操作人、操作时间（yyyy-mm-dd hh:mm:ss）、所属模块（角色管理）、操作类型（导出）
-2. 受影响对象：对应标识</t>
+          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
+2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为导出
+3. 内容详情显示导出数量、导出环境，且与实际导出操作一致
+4. 导出数据列表中每条数据包含角色名称、角色编号、状态、菜单权限、按钮权限、分配用户、数据权限、已选产品
+5. 按钮权限记录格式为菜单权限1（按钮1、按钮2）、菜单权限2（按钮3、按钮4）</t>
         </is>
       </c>
       <c r="K28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、priority_rules.md-P0</t>
         </is>
       </c>
       <c r="L28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M28" t="inlineStr" s="2">
@@ -2505,12 +2550,12 @@
       </c>
       <c r="D29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">查看导出角色的审计追踪详情，验证导出数量、环境及数据列表正确</t>
+          <t xml:space="preserve">导出角色成功，审计追踪列表新增对应记录</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="2">
@@ -2525,21 +2570,22 @@
       </c>
       <c r="H29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色导出权限和审计追踪查看权限
-2. 已成功导出角色数据</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理菜单权限、角色导出按钮权限和审计追踪菜单权限
+2. 角色管理列表存在可导出的角色数据</t>
         </is>
       </c>
       <c r="I29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入审计追踪，点击导出记录受影响对象</t>
+          <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
+2. 勾选角色并导出成功
+3. 进入审计追踪模块查看列表</t>
         </is>
       </c>
       <c r="J29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 详情弹窗基本信息：操作人、操作时间、操作模块（角色管理）、操作类型（导出）显示正确
-2. 内容详情：导出数量与实际条数一致、导出环境ip显示正确
-3. 导出数据列表：每条角色包含角色名称、角色编号、状态、菜单权限、按钮权限、分配用户、数据权限、已选产品
-4. 按钮权限格式：菜单权限1（按钮1、按钮2）、菜单权限2（按钮3、按钮4）</t>
+          <t xml:space="preserve">1. 审计追踪列表第一行新增角色管理记录
+2. 操作人为当前用户姓名；操作时间格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理
+3. 操作类型为导出；受影响对象为角色导出记录</t>
         </is>
       </c>
       <c r="K29" t="inlineStr" s="2">
@@ -2591,7 +2637,7 @@
       </c>
       <c r="D30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出导出角色的审计追踪详情为 PDF，验证导出内容一致</t>
+          <t xml:space="preserve">导出导出角色审计追踪详情为 PDF，验证导出内容一致</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -2611,19 +2657,22 @@
       </c>
       <c r="H30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有角色导出权限和审计追踪导出权限</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限
+2. 审计追踪列表存在角色管理导出记录</t>
         </is>
       </c>
       <c r="I30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 导出角色成功后，进入审计追踪点击对应记录受影响对象
-2. 点击详情页导出按钮</t>
+          <t xml:space="preserve">1. 进入审计追踪模块
+2. 点击导出记录的受影响对象查看详情
+3. 点击详情页导出按钮
+4. 打开下载的 PDF 文件</t>
         </is>
       </c>
       <c r="J30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 下载 pdf 文件到本地，文件名：&lt;受影响对象&gt;.pdf
-2. 导出内容与页面详情展示一致，包含导出数量、导出环境和数据列表</t>
+          <t xml:space="preserve">1. 下载 PDF 文件到本地，文件名为&lt;受影响对象&gt;.pdf
+2. PDF 中导出数量、导出环境和导出数据列表与页面详情展示一致</t>
         </is>
       </c>
       <c r="K30" t="inlineStr" s="2">
@@ -2675,7 +2724,7 @@
       </c>
       <c r="D31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">操作类型下拉选项包含角色管理所有操作类型</t>
+          <t xml:space="preserve">操作类型下拉选项包含角色管理全部操作类型</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -2695,29 +2744,29 @@
       </c>
       <c r="H31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有审计追踪查看权限</t>
+          <t xml:space="preserve">普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限</t>
         </is>
       </c>
       <c r="I31" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入审计追踪模块
 2. 所属模块选择角色管理
-3. 展开操作类型下拉</t>
+3. 展开操作类型下拉框</t>
         </is>
       </c>
       <c r="J31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">操作类型下拉选项显示：新增、编辑、删除、批量删除、配置、启用、停用、导入、导出</t>
+          <t xml:space="preserve">操作类型下拉选项显示新增、编辑、删除、批量删除、配置、启用、停用、导入、导出</t>
         </is>
       </c>
       <c r="K31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M31" t="inlineStr" s="2">
@@ -2779,25 +2828,26 @@
       </c>
       <c r="H32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有审计追踪查看权限
-2. 审计追踪已有角色管理及其他模块的操作记录</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限
+2. 审计追踪列表已有角色管理和其他模块的审计记录</t>
         </is>
       </c>
       <c r="I32" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入审计追踪模块
-2. 所属模块选择角色管理</t>
+2. 所属模块选择角色管理
+3. 点击搜索</t>
         </is>
       </c>
       <c r="J32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 搜索条件中模块显示为角色管理
+          <t xml:space="preserve">1. 搜索条件中所属模块保持为角色管理
 2. 列表仅展示所属模块为角色管理的审计记录</t>
         </is>
       </c>
       <c r="K32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L32" t="inlineStr" s="2">
@@ -2844,7 +2894,7 @@
       </c>
       <c r="D33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">组合搜索模块、操作类型、受影响对象，搜索结果正确</t>
+          <t xml:space="preserve">组合搜索角色管理审计记录，搜索结果正确</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -2864,25 +2914,27 @@
       </c>
       <c r="H33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 已登录业务站点，当前用户具有审计追踪查看权限
-2. 审计追踪已有角色管理相关记录</t>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限
+2. 审计追踪列表已有多个角色管理操作类型和多个受影响对象记录</t>
         </is>
       </c>
       <c r="I33" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入审计追踪模块
-2. 组合筛选：所属模块（角色管理）、操作类型（如删除）、受影响对象关键字</t>
+2. 选择所属模块为角色管理
+3. 选择操作类型为删除
+4. 输入受影响对象关键字并点击搜索</t>
         </is>
       </c>
       <c r="J33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 搜索条件保持已选值
-2. 列表仅展示同时满足三个条件的记录</t>
+          <t xml:space="preserve">1. 搜索条件保持已选模块、操作类型和受影响对象关键字
+2. 列表仅展示同时满足角色管理、删除、受影响对象关键字的审计记录</t>
         </is>
       </c>
       <c r="K33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L33" t="inlineStr" s="2">
@@ -2911,7 +2963,94 @@
         </is>
       </c>
     </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">权限控制</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">无审计追踪菜单权限，角色管理审计数据不可访问</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">权限</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理菜单权限但无审计追踪菜单权限
+2. 角色管理模块已有新增、编辑、删除等审计记录</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 查看业务站点菜单
+2. 通过审计追踪 URL 或接口直接访问角色管理审计列表
+3. 直接访问某条角色管理审计详情或详情导出接口</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 页面不展示审计追踪菜单入口
+2. URL 或接口访问被拦截，不返回角色管理审计列表数据
+3. 审计追踪详情和 PDF 导出接口均不可访问，不泄露审计数据</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：audit_trail_coverage_rules.md、user_roles.md</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">一般</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P33"/>
+  <autoFilter ref="A1:P34"/>
 </worksheet>
 </file>
--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/audit_trail_role_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/audit_trail_role_testcases.xlsx
@@ -77,7 +77,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -197,138 +197,138 @@
       </c>
       <c r="D2" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">查看新增角色审计追踪详情，验证数据正确</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">正例</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理新增按钮权限和审计追踪菜单权限
+2. 系统已存在新增成功的角色 R，角色名称、角色编号和状态均有明确值</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 进入业务站点审计追踪模块
+2. 按所属模块角色管理、操作类型新增筛选记录
+3. 点击新增记录的受影响对象查看详情</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
+2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为新增
+3. 内容详情显示角色名称、角色编号、状态，且与新增角色 R 一致</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">一般</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="64" customHeight="1">
+      <c r="A3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">新增角色成功，审计追踪列表新增对应记录</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr" s="2">
+      <c r="E3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr" s="2">
+      <c r="F3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">正例</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr" s="2">
+      <c r="H3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">普通用户已登录业务站点 A，所属启用角色拥有角色管理菜单权限、角色新增按钮权限和审计追踪菜单权限</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr" s="2">
+      <c r="I3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
 2. 新增角色 R 并保存成功
-3. 进入审计追踪模块查看列表</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr" s="2">
+3. 进入业务站点审计追踪模块查看列表</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 审计追踪列表第一行新增角色管理记录
 2. 操作人为当前用户姓名；操作时间格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理
 3. 操作类型为新增；受影响对象为新增的角色名称</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr" s="2">
+      <c r="K3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">简单</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="64" customHeight="1">
-      <c r="A3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">查看新增角色审计追踪详情，验证数据正确</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">正例</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理新增按钮权限和审计追踪菜单权限
-2. 系统已存在新增成功的角色 R，角色名称、角色编号和状态均有明确值</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 进入审计追踪模块
-2. 按所属模块角色管理、操作类型新增筛选记录
-3. 点击新增记录的受影响对象查看详情</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
-2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为新增
-3. 内容详情显示角色名称、角色编号、状态，且与新增角色 R 一致</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M3" t="inlineStr" s="2">
@@ -396,7 +396,7 @@
       </c>
       <c r="I4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入审计追踪模块
+          <t xml:space="preserve">1. 进入业务站点审计追踪模块
 2. 点击新增记录的受影响对象查看详情
 3. 点击详情页导出按钮
 4. 打开下载的 PDF 文件</t>
@@ -485,7 +485,7 @@
         <is>
           <t xml:space="preserve">1. 进入角色管理列表页
 2. 修改角色 R 的角色名称并保存成功
-3. 进入审计追踪模块，点击编辑记录的受影响对象查看详情</t>
+3. 进入业务站点审计追踪模块，点击编辑记录的受影响对象查看详情</t>
         </is>
       </c>
       <c r="J5" t="inlineStr" s="2">
@@ -573,7 +573,7 @@
         <is>
           <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
 2. 编辑角色 R 的角色名称并保存成功
-3. 进入审计追踪模块查看列表</t>
+3. 进入业务站点审计追踪模块查看列表</t>
         </is>
       </c>
       <c r="J6" t="inlineStr" s="2">
@@ -585,7 +585,7 @@
       </c>
       <c r="K6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L6" t="inlineStr" s="2">
@@ -659,7 +659,7 @@
       <c r="I7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入角色管理编辑页，不修改任何字段直接保存或取消
-2. 进入审计追踪模块查看角色管理记录</t>
+2. 进入业务站点审计追踪模块查看角色管理记录</t>
         </is>
       </c>
       <c r="J7" t="inlineStr" s="2">
@@ -742,7 +742,7 @@
       </c>
       <c r="I8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入审计追踪模块
+          <t xml:space="preserve">1. 进入业务站点审计追踪模块
 2. 点击编辑记录的受影响对象查看详情
 3. 点击详情页导出按钮
 4. 打开下载的 PDF 文件</t>
@@ -831,7 +831,7 @@
         <is>
           <t xml:space="preserve">1. 进入角色管理列表页
 2. 删除角色 R 并确认成功
-3. 进入审计追踪模块，点击删除记录的受影响对象查看详情</t>
+3. 进入业务站点审计追踪模块，点击删除记录的受影响对象查看详情</t>
         </is>
       </c>
       <c r="J9" t="inlineStr" s="2">
@@ -920,7 +920,7 @@
         <is>
           <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
 2. 删除角色 R 并确认成功
-3. 进入审计追踪模块查看列表</t>
+3. 进入业务站点审计追踪模块查看列表</t>
         </is>
       </c>
       <c r="J10" t="inlineStr" s="2">
@@ -932,7 +932,7 @@
       </c>
       <c r="K10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L10" t="inlineStr" s="2">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="I11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入审计追踪模块
+          <t xml:space="preserve">1. 进入业务站点审计追踪模块
 2. 点击删除记录的受影响对象查看详情
 3. 点击详情页导出按钮
 4. 打开下载的 PDF 文件</t>
@@ -1094,7 +1094,7 @@
         <is>
           <t xml:space="preserve">1. 进入角色管理列表页
 2. 勾选多个角色并批量删除成功
-3. 进入审计追踪模块，点击批量删除记录的受影响对象查看详情</t>
+3. 进入业务站点审计追踪模块，点击批量删除记录的受影响对象查看详情</t>
         </is>
       </c>
       <c r="J12" t="inlineStr" s="2">
@@ -1183,19 +1183,19 @@
         <is>
           <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
 2. 勾选多个角色并批量删除成功
-3. 进入审计追踪模块查看列表</t>
+3. 进入业务站点审计追踪模块查看列表</t>
         </is>
       </c>
       <c r="J13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 审计追踪列表第一行新增角色管理记录
+          <t xml:space="preserve">1. 审计追踪列表第一行新增角色管理批量删除记录
 2. 操作人为当前用户姓名；操作时间格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理
 3. 操作类型为批量删除；受影响对象为角色管理批量删除记录</t>
         </is>
       </c>
       <c r="K13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L13" t="inlineStr" s="2">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="I14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入审计追踪模块
+          <t xml:space="preserve">1. 进入业务站点审计追踪模块
 2. 点击批量删除记录的受影响对象查看详情
 3. 点击详情页导出按钮
 4. 打开下载的 PDF 文件</t>
@@ -1357,7 +1357,7 @@
         <is>
           <t xml:space="preserve">1. 进入角色管理配置页
 2. 配置角色 R 的功能权限、产品数据权限和分配用户并保存成功
-3. 进入审计追踪模块，点击配置记录的受影响对象查看详情</t>
+3. 进入业务站点审计追踪模块，点击配置记录的受影响对象查看详情</t>
         </is>
       </c>
       <c r="J15" t="inlineStr" s="2">
@@ -1446,7 +1446,7 @@
         <is>
           <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
 2. 配置角色 R 的功能权限、产品数据权限和分配用户并保存成功
-3. 进入审计追踪模块查看列表</t>
+3. 进入业务站点审计追踪模块查看列表</t>
         </is>
       </c>
       <c r="J16" t="inlineStr" s="2">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="K16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L16" t="inlineStr" s="2">
@@ -1532,7 +1532,7 @@
       <c r="I17" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入角色管理配置页，不修改功能权限、产品数据权限或分配用户直接保存或取消
-2. 进入审计追踪模块查看角色管理记录</t>
+2. 进入业务站点审计追踪模块查看角色管理记录</t>
         </is>
       </c>
       <c r="J17" t="inlineStr" s="2">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="I18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入审计追踪模块
+          <t xml:space="preserve">1. 进入业务站点审计追踪模块
 2. 点击配置记录的受影响对象查看详情
 3. 点击详情页导出按钮
 4. 打开下载的 PDF 文件</t>
@@ -1676,134 +1676,134 @@
       </c>
       <c r="D19" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">查看启用角色审计追踪详情，验证状态正确</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">正例</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色启用按钮权限和审计追踪菜单权限
+2. 系统已存在已启用成功的角色 R</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 进入业务站点审计追踪模块
+2. 按所属模块角色管理、操作类型启用筛选记录
+3. 点击启用记录的受影响对象查看详情</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
+2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为启用
+3. 内容详情显示角色名称、角色编号、状态，状态与启用后的角色状态一致</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">一般</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="64" customHeight="1">
+      <c r="A20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">启用角色成功，审计追踪列表新增对应记录</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr" s="2">
+      <c r="E20" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr" s="2">
+      <c r="F20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">正例</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr" s="2">
+      <c r="H20" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理菜单权限、角色启用按钮权限和审计追踪菜单权限
 2. 系统已存在停用状态角色 R</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr" s="2">
+      <c r="I20" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
 2. 启用角色 R 成功
-3. 进入审计追踪模块查看列表</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr" s="2">
+3. 进入业务站点审计追踪模块查看列表</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 审计追踪列表第一行新增角色管理记录
 2. 操作人为当前用户姓名；操作时间格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理
 3. 操作类型为启用；受影响对象为启用的角色名称</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">一般</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="64" customHeight="1">
-      <c r="A20" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">查看启用角色审计追踪详情，验证状态正确</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">正例</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色启用按钮权限和审计追踪菜单权限
-2. 系统已存在已启用成功的角色 R</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 进入审计追踪模块
-2. 按所属模块角色管理、操作类型启用筛选记录
-3. 点击启用记录的受影响对象查看详情</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
-2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为启用
-3. 内容详情显示角色名称、角色编号、状态，状态与启用后的角色状态一致</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L20" t="inlineStr" s="2">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="I21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入审计追踪模块
+          <t xml:space="preserve">1. 进入业务站点审计追踪模块
 2. 点击启用记录的受影响对象查看详情
 3. 点击详情页导出按钮
 4. 打开下载的 PDF 文件</t>
@@ -1937,134 +1937,134 @@
       </c>
       <c r="D22" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">查看停用角色审计追踪详情，验证状态正确</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">正例</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色停用按钮权限和审计追踪菜单权限
+2. 系统已存在已停用成功的角色 R</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 进入业务站点审计追踪模块
+2. 按所属模块角色管理、操作类型停用筛选记录
+3. 点击停用记录的受影响对象查看详情</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
+2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为停用
+3. 内容详情显示角色名称、角色编号、状态，状态与停用后的角色状态一致</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">一般</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="64" customHeight="1">
+      <c r="A23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">停用角色成功，审计追踪列表新增对应记录</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr" s="2">
+      <c r="E23" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr" s="2">
+      <c r="F23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">正例</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr" s="2">
+      <c r="H23" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理菜单权限、角色停用按钮权限和审计追踪菜单权限
 2. 系统已存在启用状态角色 R</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr" s="2">
+      <c r="I23" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
 2. 停用角色 R 成功
-3. 进入审计追踪模块查看列表</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr" s="2">
+3. 进入业务站点审计追踪模块查看列表</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 审计追踪列表第一行新增角色管理记录
 2. 操作人为当前用户姓名；操作时间格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理
 3. 操作类型为停用；受影响对象为停用的角色名称</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">一般</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="64" customHeight="1">
-      <c r="A23" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">查看停用角色审计追踪详情，验证状态正确</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">正例</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色停用按钮权限和审计追踪菜单权限
-2. 系统已存在已停用成功的角色 R</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 进入审计追踪模块
-2. 按所属模块角色管理、操作类型停用筛选记录
-3. 点击停用记录的受影响对象查看详情</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
-2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为停用
-3. 内容详情显示角色名称、角色编号、状态，状态与停用后的角色状态一致</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L23" t="inlineStr" s="2">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="I24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入审计追踪模块
+          <t xml:space="preserve">1. 进入业务站点审计追踪模块
 2. 点击停用记录的受影响对象查看详情
 3. 点击详情页导出按钮
 4. 打开下载的 PDF 文件</t>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="I25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入审计追踪模块
+          <t xml:space="preserve">1. 进入业务站点审计追踪模块
 2. 按所属模块角色管理、操作类型导入筛选记录
 3. 点击导入记录的受影响对象查看详情</t>
         </is>
@@ -2315,7 +2315,7 @@
         <is>
           <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
 2. 导入角色文件成功
-3. 进入审计追踪模块查看列表</t>
+3. 进入业务站点审计追踪模块查看列表</t>
         </is>
       </c>
       <c r="J26" t="inlineStr" s="2">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="K26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L26" t="inlineStr" s="2">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="I27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入审计追踪模块
+          <t xml:space="preserve">1. 进入业务站点审计追踪模块
 2. 点击导入记录的受影响对象查看详情
 3. 点击详情页导出按钮
 4. 打开下载的 PDF 文件</t>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="I28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入审计追踪模块
+          <t xml:space="preserve">1. 进入业务站点审计追踪模块
 2. 按所属模块角色管理、操作类型导出筛选记录
 3. 点击导出记录的受影响对象查看详情</t>
         </is>
@@ -2578,7 +2578,7 @@
         <is>
           <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
 2. 勾选角色并导出成功
-3. 进入审计追踪模块查看列表</t>
+3. 进入业务站点审计追踪模块查看列表</t>
         </is>
       </c>
       <c r="J29" t="inlineStr" s="2">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="K29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L29" t="inlineStr" s="2">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="I30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入审计追踪模块
+          <t xml:space="preserve">1. 进入业务站点审计追踪模块
 2. 点击导出记录的受影响对象查看详情
 3. 点击详情页导出按钮
 4. 打开下载的 PDF 文件</t>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="I31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入审计追踪模块
+          <t xml:space="preserve">1. 进入业务站点审计追踪模块
 2. 所属模块选择角色管理
 3. 展开操作类型下拉框</t>
         </is>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="I32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入审计追踪模块
+          <t xml:space="preserve">1. 进入业务站点审计追踪模块
 2. 所属模块选择角色管理
 3. 点击搜索</t>
         </is>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="I33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入审计追踪模块
+          <t xml:space="preserve">1. 进入业务站点审计追踪模块
 2. 选择所属模块为角色管理
 3. 选择操作类型为删除
 4. 输入受影响对象关键字并点击搜索</t>
@@ -3050,7 +3050,94 @@
         </is>
       </c>
     </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">站点隔离</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">跨业务站点不可查看角色管理审计记录</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">权限</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 B，所属启用角色拥有业务站点 B 的审计追踪菜单权限
+2. 业务站点 A 已存在角色管理新增、删除或导入审计记录
+3. 当前用户无业务站点 A 访问权限</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 在业务站点 B 进入审计追踪模块
+2. 按所属模块角色管理搜索审计记录
+3. 通过业务站点 A 的审计追踪详情 URL 或导出接口直接访问</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 业务站点 B 审计追踪列表不展示业务站点 A 的角色管理审计记录
+2. 直接访问业务站点 A 审计详情或导出接口被拦截，不返回审计数据或 PDF 文件</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：audit_trail_coverage_rules.md、user_roles.md</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">一般</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P34"/>
+  <autoFilter ref="A1:P35"/>
 </worksheet>
 </file>
--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/audit_trail_role_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/audit_trail_role_testcases.xlsx
@@ -77,7 +77,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P37"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -197,12 +197,12 @@
       </c>
       <c r="D2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">查看新增角色审计追踪详情，验证数据正确</t>
+          <t xml:space="preserve">新增角色成功，审计追踪列表新增对应记录</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="2">
@@ -217,27 +217,28 @@
       </c>
       <c r="H2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理新增按钮权限和审计追踪菜单权限
-2. 系统已存在新增成功的角色 R，角色名称、角色编号和状态均有明确值</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备角色管理和审计追踪菜单权限
+2. 角色管理列表存在可新增角色的条件</t>
         </is>
       </c>
       <c r="I2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入业务站点审计追踪模块
-2. 按所属模块角色管理、操作类型新增筛选记录
-3. 点击新增记录的受影响对象查看详情</t>
+          <t xml:space="preserve">1. 进入业务站点 - 配置管理 - 角色管理
+2. 点击新增，填写角色名称、角色编号等信息并保存
+3. 进入业务站点 - 审计追踪
+4. 查看列表第一行记录</t>
         </is>
       </c>
       <c r="J2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
-2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为新增
-3. 内容详情显示角色名称、角色编号、状态，且与新增角色 R 一致</t>
+          <t xml:space="preserve">1. 角色保存成功，列表新增对应角色记录
+2. 审计追踪列表新增一条记录，位于第一行
+3. 记录字段：操作人为当前登录用户、操作时间为 yyyy-mm-dd hh:mm:ss 格式、操作模块为角色管理、操作类型为新增、受影响对象为新增的角色名称</t>
         </is>
       </c>
       <c r="K2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L2" t="inlineStr" s="2">
@@ -284,12 +285,12 @@
       </c>
       <c r="D3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">新增角色成功，审计追踪列表新增对应记录</t>
+          <t xml:space="preserve">查看新增角色审计追踪详情，基本信息和内容详情字段正确</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="2">
@@ -304,21 +305,22 @@
       </c>
       <c r="H3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">普通用户已登录业务站点 A，所属启用角色拥有角色管理菜单权限、角色新增按钮权限和审计追踪菜单权限</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备审计追踪菜单权限
+2. 已存在新增角色的审计追踪记录</t>
         </is>
       </c>
       <c r="I3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
-2. 新增角色 R 并保存成功
-3. 进入业务站点审计追踪模块查看列表</t>
+          <t xml:space="preserve">1. 进入业务站点 - 审计追踪
+2. 点击新增角色记录的受影响对象进入详情
+3. 查看基本信息和内容详情字段</t>
         </is>
       </c>
       <c r="J3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 审计追踪列表第一行新增角色管理记录
-2. 操作人为当前用户姓名；操作时间格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理
-3. 操作类型为新增；受影响对象为新增的角色名称</t>
+          <t xml:space="preserve">1. 详情页包含基本信息和内容详情两个分组
+2. 基本信息显示操作人、操作时间、操作模块（角色管理）、操作类型（新增）
+3. 内容详情显示角色名称、角色编号、状态（启用或停用），与新增时填写的内容一致</t>
         </is>
       </c>
       <c r="K3" t="inlineStr" s="2">
@@ -328,7 +330,7 @@
       </c>
       <c r="L3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M3" t="inlineStr" s="2">
@@ -370,7 +372,7 @@
       </c>
       <c r="D4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出新增角色审计追踪详情，验证导出内容一致</t>
+          <t xml:space="preserve">导出新增角色审计追踪详情，导出 PDF 内容与页面一致</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -390,27 +392,28 @@
       </c>
       <c r="H4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限
-2. 审计追踪列表存在角色管理新增记录</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备审计追踪菜单权限
+2. 已进入新增角色审计追踪详情页</t>
         </is>
       </c>
       <c r="I4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入业务站点审计追踪模块
-2. 点击新增记录的受影响对象查看详情
-3. 点击详情页导出按钮
-4. 打开下载的 PDF 文件</t>
+          <t xml:space="preserve">1. 进入业务站点 - 审计追踪
+2. 点击新增角色记录的受影响对象进入详情
+3. 点击导出按钮
+4. 打开导出的 PDF 文件查看内容</t>
         </is>
       </c>
       <c r="J4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 下载 PDF 文件到本地，文件名为&lt;受影响对象&gt;.pdf
-2. PDF 中基本信息和内容详情与页面详情展示一致</t>
+          <t xml:space="preserve">1. 导出成功，文件格式为 PDF
+2. 文件名为 `&lt;角色名称&gt;.pdf`
+3. PDF 内容包含基本信息和内容详情，字段值与详情页展示完全一致</t>
         </is>
       </c>
       <c r="K4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L4" t="inlineStr" s="2">
@@ -457,7 +460,7 @@
       </c>
       <c r="D5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">查看编辑角色审计追踪详情，验证新旧值对比正确</t>
+          <t xml:space="preserve">编辑角色名称成功，审计追踪列表新增对应记录</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -477,33 +480,33 @@
       </c>
       <c r="H5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理编辑按钮权限和审计追踪菜单权限
-2. 系统已存在可编辑角色 R，且已记录修改前角色名称</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备角色管理和审计追踪菜单权限
+2. 角色管理列表存在已启用的角色</t>
         </is>
       </c>
       <c r="I5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页
-2. 修改角色 R 的角色名称并保存成功
-3. 进入业务站点审计追踪模块，点击编辑记录的受影响对象查看详情</t>
+          <t xml:space="preserve">1. 进入业务站点 - 配置管理 - 角色管理
+2. 点击目标角色编辑，修改角色名称并保存
+3. 进入业务站点 - 审计追踪
+4. 查看列表第一行记录</t>
         </is>
       </c>
       <c r="J5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
-2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为编辑
-3. 内容详情显示角色编号，且角色编号不可修改但可定位被修改角色
-4. 内容详情显示角色名称修改前值和修改后值对比</t>
+          <t xml:space="preserve">1. 角色保存成功，列表对应角色名称已更新
+2. 审计追踪列表新增一条记录，位于第一行
+3. 记录字段：操作人为当前登录用户、操作时间为 yyyy-mm-dd hh:mm:ss 格式、操作模块为角色管理、操作类型为编辑、受影响对象为被编辑的角色</t>
         </is>
       </c>
       <c r="K5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、priority_rules.md-P0</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M5" t="inlineStr" s="2">
@@ -545,12 +548,12 @@
       </c>
       <c r="D6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">编辑角色成功，审计追踪列表新增对应记录</t>
+          <t xml:space="preserve">查看编辑角色审计追踪详情，角色名称新旧值对比正确</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="2">
@@ -565,22 +568,22 @@
       </c>
       <c r="H6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理菜单权限、角色编辑按钮权限和审计追踪菜单权限
-2. 系统已存在可编辑角色 R</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备审计追踪菜单权限
+2. 已存在编辑角色的审计追踪记录</t>
         </is>
       </c>
       <c r="I6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
-2. 编辑角色 R 的角色名称并保存成功
-3. 进入业务站点审计追踪模块查看列表</t>
+          <t xml:space="preserve">1. 进入业务站点 - 审计追踪
+2. 点击编辑角色记录的受影响对象进入详情
+3. 查看基本信息和内容详情字段</t>
         </is>
       </c>
       <c r="J6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 审计追踪列表第一行新增角色管理记录
-2. 操作人为当前用户姓名；操作时间格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理
-3. 操作类型为编辑；受影响对象为编辑后的角色名称</t>
+          <t xml:space="preserve">1. 基本信息显示操作人、操作时间、操作模块（角色管理）、操作类型（编辑）
+2. 内容详情显示角色编号（不允许修改，记录被修改的是哪个角色）、角色名称的新值和旧值
+3. 角色名称新值与修改后内容一致，旧值与修改前内容一致</t>
         </is>
       </c>
       <c r="K6" t="inlineStr" s="2">
@@ -632,7 +635,7 @@
       </c>
       <c r="D7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">编辑角色无实际变更，审计追踪不新增记录</t>
+          <t xml:space="preserve">【待确认】进入编辑页未修改保存，不新增审计追踪记录</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -652,29 +655,31 @@
       </c>
       <c r="H7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理编辑按钮权限和审计追踪菜单权限
-2. 系统已存在可编辑角色 R</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备角色管理和审计追踪菜单权限
+2. 角色管理列表存在已启用的角色</t>
         </is>
       </c>
       <c r="I7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理编辑页，不修改任何字段直接保存或取消
-2. 进入业务站点审计追踪模块查看角色管理记录</t>
+          <t xml:space="preserve">1. 进入业务站点 - 配置管理 - 角色管理
+2. 点击目标角色编辑，进入编辑页后不做任何修改直接保存
+3. 进入业务站点 - 审计追踪
+4. 查看列表第一行记录</t>
         </is>
       </c>
       <c r="J7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪模块不新增角色管理编辑记录</t>
+          <t xml:space="preserve">审计追踪列表不新增编辑记录；列表第一行仍为其他操作类型的记录，无新增编辑日志</t>
         </is>
       </c>
       <c r="K7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：audit_trail_coverage_rules.md</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md；说明：PRD 未明确无变更操作是否产生审计记录，按审计追踪专项规则默认不应新增</t>
         </is>
       </c>
       <c r="L7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M7" t="inlineStr" s="2">
@@ -716,7 +721,7 @@
       </c>
       <c r="D8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出编辑角色审计追踪详情，验证导出内容一致</t>
+          <t xml:space="preserve">导出编辑角色审计追踪详情，导出 PDF 内容与页面一致</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -736,27 +741,27 @@
       </c>
       <c r="H8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限
-2. 审计追踪列表存在角色管理编辑记录</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备审计追踪菜单权限
+2. 已进入编辑角色审计追踪详情页</t>
         </is>
       </c>
       <c r="I8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入业务站点审计追踪模块
-2. 点击编辑记录的受影响对象查看详情
-3. 点击详情页导出按钮
-4. 打开下载的 PDF 文件</t>
+          <t xml:space="preserve">1. 进入业务站点 - 审计追踪
+2. 点击编辑角色记录的受影响对象进入详情
+3. 点击导出按钮
+4. 打开导出的 PDF 文件查看内容</t>
         </is>
       </c>
       <c r="J8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 下载 PDF 文件到本地，文件名为&lt;受影响对象&gt;.pdf
-2. PDF 中基本信息、角色编号和角色名称新旧值对比与页面详情展示一致</t>
+          <t xml:space="preserve">1. 导出成功，文件格式为 PDF，文件名为 `&lt;角色名称&gt;.pdf`
+2. PDF 内容包含基本信息、角色编号和角色名称新旧值对比，与详情页展示完全一致</t>
         </is>
       </c>
       <c r="K8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L8" t="inlineStr" s="2">
@@ -803,7 +808,7 @@
       </c>
       <c r="D9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">查看删除角色审计追踪详情，验证权限和用户信息完整</t>
+          <t xml:space="preserve">删除角色成功，审计追踪列表新增对应记录</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -823,34 +828,33 @@
       </c>
       <c r="H9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理删除按钮权限和审计追踪菜单权限
-2. 系统已存在配置了功能权限、产品数据权限和分配用户的角色 R</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备角色管理和审计追踪菜单权限
+2. 角色管理列表存在可删除的角色，且角色已配置功能权限、产品数据权限和分配用户</t>
         </is>
       </c>
       <c r="I9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页
-2. 删除角色 R 并确认成功
-3. 进入业务站点审计追踪模块，点击删除记录的受影响对象查看详情</t>
+          <t xml:space="preserve">1. 进入业务站点 - 配置管理 - 角色管理
+2. 点击目标角色删除并确认
+3. 进入业务站点 - 审计追踪
+4. 查看列表第一行记录</t>
         </is>
       </c>
       <c r="J9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
-2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为删除
-3. 内容详情显示角色名称、角色编号、状态
-4. 功能权限详情显示格式为菜单权限（按钮权限1、按钮权限2），多个菜单权限用顿号隔开
-5. 产品数据权限详情显示数据权限、已选产品，多个产品用顿号隔开；分配用户详情显示用户部门、姓名、编号</t>
+          <t xml:space="preserve">1. 角色删除成功，列表不再显示该角色
+2. 审计追踪列表新增一条记录，位于第一行
+3. 记录字段：操作人为当前登录用户、操作时间为 yyyy-mm-dd hh:mm:ss 格式、操作模块为角色管理、操作类型为删除、受影响对象为被删除的角色名称</t>
         </is>
       </c>
       <c r="K9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、priority_rules.md-P0</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M9" t="inlineStr" s="2">
@@ -892,12 +896,12 @@
       </c>
       <c r="D10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">删除角色成功，审计追踪列表新增对应记录</t>
+          <t xml:space="preserve">查看删除角色审计追踪详情，字段和详情列表正确</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="2">
@@ -912,22 +916,25 @@
       </c>
       <c r="H10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理菜单权限、角色删除按钮权限和审计追踪菜单权限
-2. 系统已存在可删除角色 R</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备审计追踪菜单权限
+2. 已存在删除角色的审计追踪记录
+3. 被删除角色删除前已配置功能权限、产品数据权限和分配用户</t>
         </is>
       </c>
       <c r="I10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
-2. 删除角色 R 并确认成功
-3. 进入业务站点审计追踪模块查看列表</t>
+          <t xml:space="preserve">1. 进入业务站点 - 审计追踪
+2. 点击删除角色记录的受影响对象进入详情
+3. 查看基本信息和内容详情字段</t>
         </is>
       </c>
       <c r="J10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 审计追踪列表第一行新增角色管理记录
-2. 操作人为当前用户姓名；操作时间格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理
-3. 操作类型为删除；受影响对象为已删除的角色名称</t>
+          <t xml:space="preserve">1. 基本信息显示操作人、操作时间、操作模块（角色管理）、操作类型（删除）
+2. 内容详情显示角色名称、角色编号、状态
+3. 功能权限详情显示菜单权限（按钮权限），多个顿号隔开，格式如 `菜单权限1（按钮1、按钮2）、菜单权限2（按钮3、按钮4）`
+4. 产品数据权限详情显示数据权限和已选产品，多个已选产品以顿号隔开
+5. 分配用户详情显示用户部门、姓名、编号</t>
         </is>
       </c>
       <c r="K10" t="inlineStr" s="2">
@@ -937,7 +944,7 @@
       </c>
       <c r="L10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M10" t="inlineStr" s="2">
@@ -979,7 +986,7 @@
       </c>
       <c r="D11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出删除角色审计追踪详情，验证导出内容一致</t>
+          <t xml:space="preserve">导出删除角色审计追踪详情，导出 PDF 内容与页面一致</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -999,27 +1006,27 @@
       </c>
       <c r="H11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限
-2. 审计追踪列表存在角色管理删除记录</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备审计追踪菜单权限
+2. 已进入删除角色审计追踪详情页</t>
         </is>
       </c>
       <c r="I11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入业务站点审计追踪模块
-2. 点击删除记录的受影响对象查看详情
-3. 点击详情页导出按钮
-4. 打开下载的 PDF 文件</t>
+          <t xml:space="preserve">1. 进入业务站点 - 审计追踪
+2. 点击删除角色记录的受影响对象进入详情
+3. 点击导出按钮
+4. 打开导出的 PDF 文件查看内容</t>
         </is>
       </c>
       <c r="J11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 下载 PDF 文件到本地，文件名为&lt;受影响对象&gt;.pdf
-2. PDF 中基本信息、角色信息、功能权限详情、产品数据权限详情和分配用户详情与页面详情展示一致</t>
+          <t xml:space="preserve">1. 导出成功，文件格式为 PDF，文件名为 `&lt;角色名称&gt;.pdf`
+2. PDF 内容包含基本信息、角色名称/编号/状态、功能权限详情、产品数据权限详情和分配用户详情，与详情页展示完全一致</t>
         </is>
       </c>
       <c r="K11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L11" t="inlineStr" s="2">
@@ -1066,7 +1073,7 @@
       </c>
       <c r="D12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">查看批量删除角色审计追踪详情，验证删除数量和明细完整</t>
+          <t xml:space="preserve">批量删除角色成功，审计追踪列表新增对应记录</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -1086,34 +1093,33 @@
       </c>
       <c r="H12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有批量删除按钮权限和审计追踪菜单权限
-2. 系统已存在多个配置了功能权限、产品数据权限和分配用户的可删除角色</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备角色管理和审计追踪菜单权限
+2. 角色管理列表存在多条可删除的角色</t>
         </is>
       </c>
       <c r="I12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页
-2. 勾选多个角色并批量删除成功
-3. 进入业务站点审计追踪模块，点击批量删除记录的受影响对象查看详情</t>
+          <t xml:space="preserve">1. 进入业务站点 - 配置管理 - 角色管理
+2. 勾选多条目标角色点击批量删除并确认
+3. 进入业务站点 - 审计追踪
+4. 查看列表第一行记录</t>
         </is>
       </c>
       <c r="J12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
-2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为批量删除
-3. 内容详情显示删除数量，且与实际批量删除角色数量一致
-4. 删除详情逐条显示角色名称、角色编号、状态、功能权限详情、产品数据权限详情、分配用户详情
-5. 功能权限详情格式为菜单权限（按钮权限1、按钮权限2），已选产品多个值用顿号隔开</t>
+          <t xml:space="preserve">1. 角色批量删除成功，列表不再显示被删除角色
+2. 审计追踪列表新增一条记录，位于第一行
+3. 记录字段：操作人为当前登录用户、操作时间为 yyyy-mm-dd hh:mm:ss 格式、操作模块为角色管理、操作类型为批量删除、受影响对象名称包含本次批量删除涉及的角色或批次标识</t>
         </is>
       </c>
       <c r="K12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、priority_rules.md-P0</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M12" t="inlineStr" s="2">
@@ -1155,12 +1161,12 @@
       </c>
       <c r="D13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">批量删除角色成功，审计追踪列表新增对应记录</t>
+          <t xml:space="preserve">查看批量删除角色审计追踪详情，删除数量和删除详情正确</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="2">
@@ -1175,22 +1181,22 @@
       </c>
       <c r="H13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理菜单权限、批量删除按钮权限和审计追踪菜单权限
-2. 系统已存在多个可删除角色</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备审计追踪菜单权限
+2. 已存在批量删除角色的审计追踪记录</t>
         </is>
       </c>
       <c r="I13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
-2. 勾选多个角色并批量删除成功
-3. 进入业务站点审计追踪模块查看列表</t>
+          <t xml:space="preserve">1. 进入业务站点 - 审计追踪
+2. 点击批量删除角色记录的受影响对象进入详情
+3. 查看基本信息和内容详情字段</t>
         </is>
       </c>
       <c r="J13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 审计追踪列表第一行新增角色管理批量删除记录
-2. 操作人为当前用户姓名；操作时间格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理
-3. 操作类型为批量删除；受影响对象为角色管理批量删除记录</t>
+          <t xml:space="preserve">1. 基本信息显示操作人、操作时间、操作模块（角色管理）、操作类型（批量删除）
+2. 内容详情显示删除数量，与实际批量删除的角色数一致
+3. 删除详情列表逐条显示每个角色的角色名称、角色编号、状态、功能权限详情、产品数据权限详情和分配用户详情</t>
         </is>
       </c>
       <c r="K13" t="inlineStr" s="2">
@@ -1242,7 +1248,7 @@
       </c>
       <c r="D14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出批量删除角色审计追踪详情，验证导出内容一致</t>
+          <t xml:space="preserve">【待确认】导出批量删除角色审计追踪详情，分配用户为空时展示正确</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -1257,32 +1263,34 @@
       </c>
       <c r="G14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">正例</t>
+          <t xml:space="preserve">边界</t>
         </is>
       </c>
       <c r="H14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限
-2. 审计追踪列表存在角色管理批量删除记录</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备审计追踪菜单权限
+2. 已存在批量删除角色的审计追踪记录
+3. 被删除角色中存在未分配用户的角色</t>
         </is>
       </c>
       <c r="I14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入业务站点审计追踪模块
-2. 点击批量删除记录的受影响对象查看详情
-3. 点击详情页导出按钮
-4. 打开下载的 PDF 文件</t>
+          <t xml:space="preserve">1. 进入业务站点 - 审计追踪
+2. 点击批量删除角色记录的受影响对象进入详情
+3. 点击导出按钮
+4. 打开导出的 PDF 文件查看内容</t>
         </is>
       </c>
       <c r="J14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 下载 PDF 文件到本地，文件名为&lt;受影响对象&gt;.pdf
-2. PDF 中删除数量和每条删除详情与页面详情展示一致</t>
+          <t xml:space="preserve">1. 导出成功，文件格式为 PDF
+2. PDF 内容包含基本信息、删除数量和删除详情
+3. 未分配用户的角色在分配用户详情字段按产品实际样式展示（空字符串、横线或"无"）</t>
         </is>
       </c>
       <c r="K14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md；说明：PRD 未明确分配用户为空时的展示样式，需要确认</t>
         </is>
       </c>
       <c r="L14" t="inlineStr" s="2">
@@ -1329,7 +1337,7 @@
       </c>
       <c r="D15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">查看配置角色审计追踪详情，验证权限和用户信息完整</t>
+          <t xml:space="preserve">配置角色权限成功，审计追踪列表新增对应记录</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -1349,34 +1357,33 @@
       </c>
       <c r="H15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色配置按钮权限和审计追踪菜单权限
-2. 系统已存在已配置功能权限、产品数据权限和分配用户的角色 R</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备角色管理和审计追踪菜单权限
+2. 角色管理列表存在已启用的角色，且角色已有部分权限配置</t>
         </is>
       </c>
       <c r="I15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理配置页
-2. 配置角色 R 的功能权限、产品数据权限和分配用户并保存成功
-3. 进入业务站点审计追踪模块，点击配置记录的受影响对象查看详情</t>
+          <t xml:space="preserve">1. 进入业务站点 - 配置管理 - 角色管理
+2. 点击目标角色配置，修改功能权限、产品数据权限或分配用户并保存
+3. 进入业务站点 - 审计追踪
+4. 查看列表第一行记录</t>
         </is>
       </c>
       <c r="J15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
-2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为配置
-3. 内容详情显示角色名称、角色编号、状态
-4. 功能权限详情显示格式为菜单权限（按钮权限1、按钮权限2），多个菜单权限用顿号隔开
-5. 产品数据权限详情显示数据权限、已选产品，多个产品用顿号隔开；分配用户详情显示用户部门、姓名、编号</t>
+          <t xml:space="preserve">1. 配置保存成功
+2. 审计追踪列表新增一条记录，位于第一行
+3. 记录字段：操作人为当前登录用户、操作时间为 yyyy-mm-dd hh:mm:ss 格式、操作模块为角色管理、操作类型为配置、受影响对象为被配置的角色</t>
         </is>
       </c>
       <c r="K15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、priority_rules.md-P0</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M15" t="inlineStr" s="2">
@@ -1418,12 +1425,12 @@
       </c>
       <c r="D16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置角色权限成功，审计追踪列表新增对应记录</t>
+          <t xml:space="preserve">查看配置角色审计追踪详情，权限/数据/用户详情正确</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="2">
@@ -1438,22 +1445,24 @@
       </c>
       <c r="H16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理菜单权限、角色配置按钮权限和审计追踪菜单权限
-2. 系统已存在可配置角色 R</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备审计追踪菜单权限
+2. 已存在配置角色的审计追踪记录</t>
         </is>
       </c>
       <c r="I16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
-2. 配置角色 R 的功能权限、产品数据权限和分配用户并保存成功
-3. 进入业务站点审计追踪模块查看列表</t>
+          <t xml:space="preserve">1. 进入业务站点 - 审计追踪
+2. 点击配置角色记录的受影响对象进入详情
+3. 查看基本信息和内容详情字段</t>
         </is>
       </c>
       <c r="J16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 审计追踪列表第一行新增角色管理记录
-2. 操作人为当前用户姓名；操作时间格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理
-3. 操作类型为配置；受影响对象为配置的角色名称</t>
+          <t xml:space="preserve">1. 基本信息显示操作人、操作时间、操作模块（角色管理）、操作类型（配置）
+2. 内容详情显示角色名称、角色编号、状态
+3. 功能权限详情显示菜单权限（按钮权限），多个顿号隔开
+4. 产品数据权限详情显示数据权限和已选产品
+5. 分配用户详情显示用户部门、姓名、编号</t>
         </is>
       </c>
       <c r="K16" t="inlineStr" s="2">
@@ -1463,7 +1472,7 @@
       </c>
       <c r="L16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M16" t="inlineStr" s="2">
@@ -1505,7 +1514,7 @@
       </c>
       <c r="D17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置角色无实际变更，审计追踪不新增记录</t>
+          <t xml:space="preserve">【待确认】进入配置页未修改保存，不新增审计追踪记录</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -1525,29 +1534,31 @@
       </c>
       <c r="H17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色配置按钮权限和审计追踪菜单权限
-2. 系统已存在可配置角色 R</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备角色管理和审计追踪菜单权限
+2. 角色管理列表存在已启用的角色</t>
         </is>
       </c>
       <c r="I17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理配置页，不修改功能权限、产品数据权限或分配用户直接保存或取消
-2. 进入业务站点审计追踪模块查看角色管理记录</t>
+          <t xml:space="preserve">1. 进入业务站点 - 配置管理 - 角色管理
+2. 点击目标角色配置，进入配置页后不做任何修改直接保存
+3. 进入业务站点 - 审计追踪
+4. 查看列表第一行记录</t>
         </is>
       </c>
       <c r="J17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪模块不新增角色管理配置记录</t>
+          <t xml:space="preserve">审计追踪列表不新增配置记录；列表第一行仍为其他操作类型的记录，无新增配置日志</t>
         </is>
       </c>
       <c r="K17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：audit_trail_coverage_rules.md</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md；说明：PRD 未明确无变更操作是否产生审计记录，按审计追踪专项规则默认不应新增</t>
         </is>
       </c>
       <c r="L17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M17" t="inlineStr" s="2">
@@ -1589,7 +1600,7 @@
       </c>
       <c r="D18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出配置角色审计追踪详情，验证导出内容一致</t>
+          <t xml:space="preserve">导出配置角色审计追踪详情，导出 PDF 内容与页面一致</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -1609,27 +1620,27 @@
       </c>
       <c r="H18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限
-2. 审计追踪列表存在角色管理配置记录</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备审计追踪菜单权限
+2. 已进入配置角色审计追踪详情页</t>
         </is>
       </c>
       <c r="I18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入业务站点审计追踪模块
-2. 点击配置记录的受影响对象查看详情
-3. 点击详情页导出按钮
-4. 打开下载的 PDF 文件</t>
+          <t xml:space="preserve">1. 进入业务站点 - 审计追踪
+2. 点击配置角色记录的受影响对象进入详情
+3. 点击导出按钮
+4. 打开导出的 PDF 文件查看内容</t>
         </is>
       </c>
       <c r="J18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 下载 PDF 文件到本地，文件名为&lt;受影响对象&gt;.pdf
-2. PDF 中角色信息、功能权限详情、产品数据权限详情和分配用户详情与页面详情展示一致</t>
+          <t xml:space="preserve">1. 导出成功，文件格式为 PDF，文件名为 `&lt;角色名称&gt;.pdf`
+2. PDF 内容包含基本信息、角色名称/编号/状态、功能权限详情、产品数据权限详情和分配用户详情，与详情页展示完全一致</t>
         </is>
       </c>
       <c r="K18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L18" t="inlineStr" s="2">
@@ -1676,12 +1687,12 @@
       </c>
       <c r="D19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">查看启用角色审计追踪详情，验证状态正确</t>
+          <t xml:space="preserve">启用角色成功，审计追踪列表新增对应记录</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="2">
@@ -1696,27 +1707,28 @@
       </c>
       <c r="H19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色启用按钮权限和审计追踪菜单权限
-2. 系统已存在已启用成功的角色 R</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备角色管理和审计追踪菜单权限
+2. 角色管理列表存在已停用的角色</t>
         </is>
       </c>
       <c r="I19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入业务站点审计追踪模块
-2. 按所属模块角色管理、操作类型启用筛选记录
-3. 点击启用记录的受影响对象查看详情</t>
+          <t xml:space="preserve">1. 进入业务站点 - 配置管理 - 角色管理
+2. 点击目标角色启用并确认
+3. 进入业务站点 - 审计追踪
+4. 查看列表第一行记录</t>
         </is>
       </c>
       <c r="J19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
-2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为启用
-3. 内容详情显示角色名称、角色编号、状态，状态与启用后的角色状态一致</t>
+          <t xml:space="preserve">1. 角色启用成功，列表对应角色状态变为启用
+2. 审计追踪列表新增一条记录，位于第一行
+3. 记录字段：操作人为当前登录用户、操作时间为 yyyy-mm-dd hh:mm:ss 格式、操作模块为角色管理、操作类型为启用、受影响对象为被启用的角色</t>
         </is>
       </c>
       <c r="K19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L19" t="inlineStr" s="2">
@@ -1763,12 +1775,12 @@
       </c>
       <c r="D20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">启用角色成功，审计追踪列表新增对应记录</t>
+          <t xml:space="preserve">查看启用角色审计追踪详情，基本信息和内容详情字段正确</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="2">
@@ -1783,22 +1795,21 @@
       </c>
       <c r="H20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理菜单权限、角色启用按钮权限和审计追踪菜单权限
-2. 系统已存在停用状态角色 R</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备审计追踪菜单权限
+2. 已存在启用角色的审计追踪记录</t>
         </is>
       </c>
       <c r="I20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
-2. 启用角色 R 成功
-3. 进入业务站点审计追踪模块查看列表</t>
+          <t xml:space="preserve">1. 进入业务站点 - 审计追踪
+2. 点击启用角色记录的受影响对象进入详情
+3. 查看基本信息和内容详情字段</t>
         </is>
       </c>
       <c r="J20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 审计追踪列表第一行新增角色管理记录
-2. 操作人为当前用户姓名；操作时间格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理
-3. 操作类型为启用；受影响对象为启用的角色名称</t>
+          <t xml:space="preserve">1. 基本信息显示操作人、操作时间、操作模块（角色管理）、操作类型（启用）
+2. 内容详情显示角色名称、角色编号、状态（启用）</t>
         </is>
       </c>
       <c r="K20" t="inlineStr" s="2">
@@ -1850,7 +1861,7 @@
       </c>
       <c r="D21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出启用角色审计追踪详情，验证导出内容一致</t>
+          <t xml:space="preserve">导出启用角色审计追踪详情，导出 PDF 内容与页面一致</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -1870,27 +1881,27 @@
       </c>
       <c r="H21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限
-2. 审计追踪列表存在角色管理启用记录</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备审计追踪菜单权限
+2. 已进入启用角色审计追踪详情页</t>
         </is>
       </c>
       <c r="I21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入业务站点审计追踪模块
-2. 点击启用记录的受影响对象查看详情
-3. 点击详情页导出按钮
-4. 打开下载的 PDF 文件</t>
+          <t xml:space="preserve">1. 进入业务站点 - 审计追踪
+2. 点击启用角色记录的受影响对象进入详情
+3. 点击导出按钮
+4. 打开导出的 PDF 文件查看内容</t>
         </is>
       </c>
       <c r="J21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 下载 PDF 文件到本地，文件名为&lt;受影响对象&gt;.pdf
-2. PDF 中基本信息、角色名称、角色编号和状态与页面详情展示一致</t>
+          <t xml:space="preserve">1. 导出成功，文件格式为 PDF，文件名为 `&lt;角色名称&gt;.pdf`
+2. PDF 内容包含基本信息和内容详情，字段值与详情页展示完全一致</t>
         </is>
       </c>
       <c r="K21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L21" t="inlineStr" s="2">
@@ -1937,12 +1948,12 @@
       </c>
       <c r="D22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">查看停用角色审计追踪详情，验证状态正确</t>
+          <t xml:space="preserve">停用角色成功，审计追踪列表新增对应记录</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="2">
@@ -1957,27 +1968,28 @@
       </c>
       <c r="H22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色停用按钮权限和审计追踪菜单权限
-2. 系统已存在已停用成功的角色 R</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备角色管理和审计追踪菜单权限
+2. 角色管理列表存在已启用的角色</t>
         </is>
       </c>
       <c r="I22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入业务站点审计追踪模块
-2. 按所属模块角色管理、操作类型停用筛选记录
-3. 点击停用记录的受影响对象查看详情</t>
+          <t xml:space="preserve">1. 进入业务站点 - 配置管理 - 角色管理
+2. 点击目标角色停用并确认
+3. 进入业务站点 - 审计追踪
+4. 查看列表第一行记录</t>
         </is>
       </c>
       <c r="J22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
-2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为停用
-3. 内容详情显示角色名称、角色编号、状态，状态与停用后的角色状态一致</t>
+          <t xml:space="preserve">1. 角色停用成功，列表对应角色状态变为停用
+2. 审计追踪列表新增一条记录，位于第一行
+3. 记录字段：操作人为当前登录用户、操作时间为 yyyy-mm-dd hh:mm:ss 格式、操作模块为角色管理、操作类型为停用、受影响对象为被停用的角色</t>
         </is>
       </c>
       <c r="K22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L22" t="inlineStr" s="2">
@@ -2024,12 +2036,12 @@
       </c>
       <c r="D23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">停用角色成功，审计追踪列表新增对应记录</t>
+          <t xml:space="preserve">查看停用角色审计追踪详情，基本信息和内容详情字段正确</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="2">
@@ -2044,22 +2056,21 @@
       </c>
       <c r="H23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理菜单权限、角色停用按钮权限和审计追踪菜单权限
-2. 系统已存在启用状态角色 R</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备审计追踪菜单权限
+2. 已存在停用角色的审计追踪记录</t>
         </is>
       </c>
       <c r="I23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
-2. 停用角色 R 成功
-3. 进入业务站点审计追踪模块查看列表</t>
+          <t xml:space="preserve">1. 进入业务站点 - 审计追踪
+2. 点击停用角色记录的受影响对象进入详情
+3. 查看基本信息和内容详情字段</t>
         </is>
       </c>
       <c r="J23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 审计追踪列表第一行新增角色管理记录
-2. 操作人为当前用户姓名；操作时间格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理
-3. 操作类型为停用；受影响对象为停用的角色名称</t>
+          <t xml:space="preserve">1. 基本信息显示操作人、操作时间、操作模块（角色管理）、操作类型（停用）
+2. 内容详情显示角色名称、角色编号、状态（停用）</t>
         </is>
       </c>
       <c r="K23" t="inlineStr" s="2">
@@ -2111,7 +2122,7 @@
       </c>
       <c r="D24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出停用角色审计追踪详情，验证导出内容一致</t>
+          <t xml:space="preserve">导出停用角色审计追踪详情，导出 PDF 内容与页面一致</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -2131,27 +2142,27 @@
       </c>
       <c r="H24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限
-2. 审计追踪列表存在角色管理停用记录</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备审计追踪菜单权限
+2. 已进入停用角色审计追踪详情页</t>
         </is>
       </c>
       <c r="I24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入业务站点审计追踪模块
-2. 点击停用记录的受影响对象查看详情
-3. 点击详情页导出按钮
-4. 打开下载的 PDF 文件</t>
+          <t xml:space="preserve">1. 进入业务站点 - 审计追踪
+2. 点击停用角色记录的受影响对象进入详情
+3. 点击导出按钮
+4. 打开导出的 PDF 文件查看内容</t>
         </is>
       </c>
       <c r="J24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 下载 PDF 文件到本地，文件名为&lt;受影响对象&gt;.pdf
-2. PDF 中基本信息、角色名称、角色编号和状态与页面详情展示一致</t>
+          <t xml:space="preserve">1. 导出成功，文件格式为 PDF，文件名为 `&lt;角色名称&gt;.pdf`
+2. PDF 内容包含基本信息和内容详情，字段值与详情页展示完全一致</t>
         </is>
       </c>
       <c r="K24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L24" t="inlineStr" s="2">
@@ -2198,7 +2209,7 @@
       </c>
       <c r="D25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">查看导入角色审计追踪详情，验证文件名、数量和数据列表正确</t>
+          <t xml:space="preserve">导入角色成功，审计追踪列表新增对应记录</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -2218,29 +2229,28 @@
       </c>
       <c r="H25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色导入按钮权限和审计追踪菜单权限
-2. 系统已成功导入包含多条角色数据的 Excel 文件</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备角色管理和审计追踪菜单权限
+2. 已准备可成功导入的角色模板文件，文件包含多条角色数据</t>
         </is>
       </c>
       <c r="I25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入业务站点审计追踪模块
-2. 按所属模块角色管理、操作类型导入筛选记录
-3. 点击导入记录的受影响对象查看详情</t>
+          <t xml:space="preserve">1. 进入业务站点 - 配置管理 - 角色管理
+2. 点击导入，上传模板文件并完成导入
+3. 进入业务站点 - 审计追踪
+4. 查看列表第一行记录</t>
         </is>
       </c>
       <c r="J25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
-2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为导入
-3. 内容详情显示导入文件名、导入数量，且与实际导入文件一致
-4. 导入数据列表中每条数据包含角色名称、角色编号、状态、菜单权限、按钮权限、分配用户、数据权限、已选产品
-5. 按钮权限记录格式为菜单权限1（按钮1、按钮2）、菜单权限2（按钮3、按钮4）</t>
+          <t xml:space="preserve">1. 角色导入成功，列表新增对应角色记录
+2. 审计追踪列表新增一条记录，位于第一行
+3. 记录字段：操作人为当前登录用户、操作时间为 yyyy-mm-dd hh:mm:ss 格式、操作模块为角色管理、操作类型为导入、受影响对象按导入文件名或导入批次命名</t>
         </is>
       </c>
       <c r="K25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、priority_rules.md-P0</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md、role_manage_import_export_template.md</t>
         </is>
       </c>
       <c r="L25" t="inlineStr" s="2">
@@ -2287,12 +2297,12 @@
       </c>
       <c r="D26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入角色成功，审计追踪列表新增对应记录</t>
+          <t xml:space="preserve">查看导入角色审计追踪详情，导入数量和数据列表正确</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="2">
@@ -2307,27 +2317,27 @@
       </c>
       <c r="H26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理菜单权限、角色导入按钮权限和审计追踪菜单权限
-2. 已准备合法的角色导入 Excel 文件</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备审计追踪菜单权限
+2. 已存在导入角色的审计追踪记录</t>
         </is>
       </c>
       <c r="I26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
-2. 导入角色文件成功
-3. 进入业务站点审计追踪模块查看列表</t>
+          <t xml:space="preserve">1. 进入业务站点 - 审计追踪
+2. 点击导入角色记录的受影响对象进入详情
+3. 查看基本信息和内容详情字段</t>
         </is>
       </c>
       <c r="J26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 审计追踪列表第一行新增角色管理记录
-2. 操作人为当前用户姓名；操作时间格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理
-3. 操作类型为导入；受影响对象为导入文件名</t>
+          <t xml:space="preserve">1. 基本信息显示操作人、操作时间、操作模块（角色管理）、操作类型（导入）
+2. 内容详情显示导入文件名、导入数量
+3. 导入数据列表逐条显示角色名称、角色编号、状态、菜单权限、按钮权限、分配用户、数据权限、已选产品</t>
         </is>
       </c>
       <c r="K26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md、role_manage_import_export_template.md</t>
         </is>
       </c>
       <c r="L26" t="inlineStr" s="2">
@@ -2374,7 +2384,7 @@
       </c>
       <c r="D27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出导入角色审计追踪详情，验证导出内容一致</t>
+          <t xml:space="preserve">导出导入角色审计追踪详情，导出 PDF 内容与页面一致</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -2394,27 +2404,27 @@
       </c>
       <c r="H27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限
-2. 审计追踪列表存在角色管理导入记录</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备审计追踪菜单权限
+2. 已进入导入角色审计追踪详情页</t>
         </is>
       </c>
       <c r="I27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入业务站点审计追踪模块
-2. 点击导入记录的受影响对象查看详情
-3. 点击详情页导出按钮
-4. 打开下载的 PDF 文件</t>
+          <t xml:space="preserve">1. 进入业务站点 - 审计追踪
+2. 点击导入角色记录的受影响对象进入详情
+3. 点击导出按钮
+4. 打开导出的 PDF 文件查看内容</t>
         </is>
       </c>
       <c r="J27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 下载 PDF 文件到本地，文件名为&lt;受影响对象&gt;.pdf
-2. PDF 中导入文件名、导入数量和导入数据列表与页面详情展示一致</t>
+          <t xml:space="preserve">1. 导出成功，文件格式为 PDF
+2. PDF 内容包含基本信息、导入文件名、导入数量和导入数据列表，与详情页展示完全一致</t>
         </is>
       </c>
       <c r="K27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L27" t="inlineStr" s="2">
@@ -2461,7 +2471,7 @@
       </c>
       <c r="D28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">查看导出角色审计追踪详情，验证数量、环境和数据列表正确</t>
+          <t xml:space="preserve">导出角色成功，审计追踪列表新增对应记录</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -2481,34 +2491,33 @@
       </c>
       <c r="H28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色导出按钮权限和审计追踪菜单权限
-2. 系统已成功导出多条角色数据</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备角色管理和审计追踪菜单权限
+2. 角色管理列表存在多条可导出的角色</t>
         </is>
       </c>
       <c r="I28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入业务站点审计追踪模块
-2. 按所属模块角色管理、操作类型导出筛选记录
-3. 点击导出记录的受影响对象查看详情</t>
+          <t xml:space="preserve">1. 进入业务站点 - 配置管理 - 角色管理
+2. 勾选多条目标角色点击导出
+3. 进入业务站点 - 审计追踪
+4. 查看列表第一行记录</t>
         </is>
       </c>
       <c r="J28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 审计追踪详情包含基本信息和内容详情
-2. 基本信息显示操作人、操作时间；操作模块为角色管理；操作类型为导出
-3. 内容详情显示导出数量、导出环境，且与实际导出操作一致
-4. 导出数据列表中每条数据包含角色名称、角色编号、状态、菜单权限、按钮权限、分配用户、数据权限、已选产品
-5. 按钮权限记录格式为菜单权限1（按钮1、按钮2）、菜单权限2（按钮3、按钮4）</t>
+          <t xml:space="preserve">1. 角色导出成功，下载导出文件
+2. 审计追踪列表新增一条记录，位于第一行
+3. 记录字段：操作人为当前登录用户、操作时间为 yyyy-mm-dd hh:mm:ss 格式、操作模块为角色管理、操作类型为导出、受影响对象按导出批次命名</t>
         </is>
       </c>
       <c r="K28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、priority_rules.md-P0</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md、role_manage_import_export_template.md</t>
         </is>
       </c>
       <c r="L28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M28" t="inlineStr" s="2">
@@ -2550,12 +2559,12 @@
       </c>
       <c r="D29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出角色成功，审计追踪列表新增对应记录</t>
+          <t xml:space="preserve">查看导出角色审计追踪详情，导出数量/环境/数据列表正确</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="2">
@@ -2570,27 +2579,27 @@
       </c>
       <c r="H29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理菜单权限、角色导出按钮权限和审计追踪菜单权限
-2. 角色管理列表存在可导出的角色数据</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备审计追踪菜单权限
+2. 已存在导出角色的审计追踪记录</t>
         </is>
       </c>
       <c r="I29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
-2. 勾选角色并导出成功
-3. 进入业务站点审计追踪模块查看列表</t>
+          <t xml:space="preserve">1. 进入业务站点 - 审计追踪
+2. 点击导出角色记录的受影响对象进入详情
+3. 查看基本信息和内容详情字段</t>
         </is>
       </c>
       <c r="J29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 审计追踪列表第一行新增角色管理记录
-2. 操作人为当前用户姓名；操作时间格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理
-3. 操作类型为导出；受影响对象为角色导出记录</t>
+          <t xml:space="preserve">1. 基本信息显示操作人、操作时间、操作模块（角色管理）、操作类型（导出）
+2. 内容详情显示导出数量、导出环境
+3. 导出数据列表逐条显示角色名称、角色编号、状态、菜单权限、按钮权限、分配用户、数据权限、已选产品</t>
         </is>
       </c>
       <c r="K29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md、role_manage_import_export_template.md</t>
         </is>
       </c>
       <c r="L29" t="inlineStr" s="2">
@@ -2637,7 +2646,7 @@
       </c>
       <c r="D30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出导出角色审计追踪详情为 PDF，验证导出内容一致</t>
+          <t xml:space="preserve">导出导出角色审计追踪详情，导出 PDF 内容与页面一致</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -2657,27 +2666,27 @@
       </c>
       <c r="H30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限
-2. 审计追踪列表存在角色管理导出记录</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备审计追踪菜单权限
+2. 已进入导出角色审计追踪详情页</t>
         </is>
       </c>
       <c r="I30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入业务站点审计追踪模块
-2. 点击导出记录的受影响对象查看详情
-3. 点击详情页导出按钮
-4. 打开下载的 PDF 文件</t>
+          <t xml:space="preserve">1. 进入业务站点 - 审计追踪
+2. 点击导出角色记录的受影响对象进入详情
+3. 点击导出按钮
+4. 打开导出的 PDF 文件查看内容</t>
         </is>
       </c>
       <c r="J30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 下载 PDF 文件到本地，文件名为&lt;受影响对象&gt;.pdf
-2. PDF 中导出数量、导出环境和导出数据列表与页面详情展示一致</t>
+          <t xml:space="preserve">1. 导出成功，文件格式为 PDF
+2. PDF 内容包含基本信息、导出数量、导出环境和导出数据列表，与详情页展示完全一致</t>
         </is>
       </c>
       <c r="K30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L30" t="inlineStr" s="2">
@@ -2724,7 +2733,7 @@
       </c>
       <c r="D31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">操作类型下拉选项包含角色管理全部操作类型</t>
+          <t xml:space="preserve">按模块筛选审计追踪列表，仅展示角色管理记录</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -2744,19 +2753,20 @@
       </c>
       <c r="H31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备审计追踪菜单权限
+2. 审计追踪列表存在多个模块的记录，其中包含角色管理</t>
         </is>
       </c>
       <c r="I31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入业务站点审计追踪模块
-2. 所属模块选择角色管理
-3. 展开操作类型下拉框</t>
+          <t xml:space="preserve">1. 进入业务站点 - 审计追踪
+2. 模块筛选条件选择角色管理
+3. 查看列表展示</t>
         </is>
       </c>
       <c r="J31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">操作类型下拉选项显示新增、编辑、删除、批量删除、配置、启用、停用、导入、导出</t>
+          <t xml:space="preserve">列表仅展示操作模块为角色管理的审计记录；其他模块记录不展示；筛选条件保持为角色管理</t>
         </is>
       </c>
       <c r="K31" t="inlineStr" s="2">
@@ -2766,7 +2776,7 @@
       </c>
       <c r="L31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M31" t="inlineStr" s="2">
@@ -2808,7 +2818,7 @@
       </c>
       <c r="D32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">按模块筛选角色管理，列表仅显示角色管理审计记录</t>
+          <t xml:space="preserve">按操作类型筛选审计追踪列表，仅展示对应类型记录</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -2828,26 +2838,26 @@
       </c>
       <c r="H32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限
-2. 审计追踪列表已有角色管理和其他模块的审计记录</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备审计追踪菜单权限
+2. 审计追踪列表存在角色管理多种操作类型的记录</t>
         </is>
       </c>
       <c r="I32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入业务站点审计追踪模块
-2. 所属模块选择角色管理
-3. 点击搜索</t>
+          <t xml:space="preserve">1. 进入业务站点 - 审计追踪
+2. 模块筛选条件选择角色管理
+3. 操作类型筛选条件分别选择新增、编辑、删除、批量删除、配置、启用、停用、导入、导出
+4. 查看列表展示</t>
         </is>
       </c>
       <c r="J32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 搜索条件中所属模块保持为角色管理
-2. 列表仅展示所属模块为角色管理的审计记录</t>
+          <t xml:space="preserve">操作类型下拉仅展示角色管理支持的 9 种操作类型，不混入其他模块操作类型；选择任一类型后列表仅展示对应类型记录</t>
         </is>
       </c>
       <c r="K32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：audit_trail_coverage_rules.md</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L32" t="inlineStr" s="2">
@@ -2894,7 +2904,7 @@
       </c>
       <c r="D33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">组合搜索角色管理审计记录，搜索结果正确</t>
+          <t xml:space="preserve">按受影响对象关键字搜索审计追踪列表</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -2914,27 +2924,25 @@
       </c>
       <c r="H33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有审计追踪菜单权限
-2. 审计追踪列表已有多个角色管理操作类型和多个受影响对象记录</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备审计追踪菜单权限
+2. 审计追踪列表存在多条角色管理记录，受影响对象包含目标关键字</t>
         </is>
       </c>
       <c r="I33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入业务站点审计追踪模块
-2. 选择所属模块为角色管理
-3. 选择操作类型为删除
-4. 输入受影响对象关键字并点击搜索</t>
+          <t xml:space="preserve">1. 进入业务站点 - 审计追踪
+2. 受影响对象搜索框输入目标角色名称关键字
+3. 查看列表展示</t>
         </is>
       </c>
       <c r="J33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 搜索条件保持已选模块、操作类型和受影响对象关键字
-2. 列表仅展示同时满足角色管理、删除、受影响对象关键字的审计记录</t>
+          <t xml:space="preserve">列表仅展示受影响对象包含该关键字的角色管理审计记录；其他记录不展示；搜索条件保持已输入关键字</t>
         </is>
       </c>
       <c r="K33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：audit_trail_coverage_rules.md</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L33" t="inlineStr" s="2">
@@ -2976,17 +2984,17 @@
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">权限控制</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">无审计追踪菜单权限，角色管理审计数据不可访问</t>
+          <t xml:space="preserve">组合搜索审计追踪列表，搜索条件保持</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="2">
@@ -2996,32 +3004,31 @@
       </c>
       <c r="G34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">权限</t>
+          <t xml:space="preserve">正例</t>
         </is>
       </c>
       <c r="H34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A，所属启用角色拥有角色管理菜单权限但无审计追踪菜单权限
-2. 角色管理模块已有新增、编辑、删除等审计记录</t>
+          <t xml:space="preserve">1. 已登录业务站点并具备审计追踪菜单权限
+2. 审计追踪列表存在多条满足组合条件的角色管理记录</t>
         </is>
       </c>
       <c r="I34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 查看业务站点菜单
-2. 通过审计追踪 URL 或接口直接访问角色管理审计列表
-3. 直接访问某条角色管理审计详情或详情导出接口</t>
+          <t xml:space="preserve">1. 进入业务站点 - 审计追踪
+2. 模块选择角色管理，操作类型选择删除，受影响对象输入目标关键字
+3. 查看列表展示
+4. 翻页或刷新页面后查看搜索条件</t>
         </is>
       </c>
       <c r="J34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 页面不展示审计追踪菜单入口
-2. URL 或接口访问被拦截，不返回角色管理审计列表数据
-3. 审计追踪详情和 PDF 导出接口均不可访问，不泄露审计数据</t>
+          <t xml:space="preserve">列表仅展示同时满足模块=角色管理、操作类型=删除、受影响对象包含关键字三个条件的记录；翻页或刷新后搜索条件保持已选值</t>
         </is>
       </c>
       <c r="K34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：audit_trail_coverage_rules.md、user_roles.md</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L34" t="inlineStr" s="2">
@@ -3063,81 +3070,256 @@
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">配置</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">审计追踪详情页字段展示校验</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">正例</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 已登录业务站点并具备审计追踪菜单权限
+2. 已存在任一角色管理操作的审计追踪记录</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 进入业务站点 - 审计追踪
+2. 点击任一角色管理记录的受影响对象进入详情
+3. 查看详情页字段展示</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 详情页顶部标题格式为"审计追踪详情 - &lt;操作类型&gt;"，右侧有关闭按钮
+2. 主内容区按基本信息和内容详情分组展示
+3. 删除、批量删除、配置操作的多条明细以表格形式展示，表头包含角色名称、角色编号、状态、功能权限详情、产品数据权限详情、分配用户详情
+4. 底部右侧显示导出按钮和关闭按钮</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd；说明：UI 图未提供，视觉细节待补充后再细化</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">困难</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">权限控制</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">无审计追踪菜单权限，入口/列表/详情/导出均不可访问</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">反例</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 已登录业务站点但不具备审计追踪菜单权限
+2. 业务站点已产生角色管理操作记录</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 查看业务站点左侧导航菜单
+2. 尝试通过 URL 直接访问审计追踪列表、详情、导出按钮或后端接口</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 左侧导航不显示审计追踪菜单入口
+2. 通过 URL 直接访问列表、详情、导出接口均被拒绝，提示无权限或重定向
+3. 不泄露任何审计数据</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md、user_roles.md</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">简单</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">站点隔离</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">跨业务站点不可查看角色管理审计记录</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr" s="2">
+      <c r="D37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">跨业务站点用户不可查看或导出角色管理审计记录</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">权限</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 B，所属启用角色拥有业务站点 B 的审计追踪菜单权限
-2. 业务站点 A 已存在角色管理新增、删除或导入审计记录
-3. 当前用户无业务站点 A 访问权限</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 在业务站点 B 进入审计追踪模块
-2. 按所属模块角色管理搜索审计记录
-3. 通过业务站点 A 的审计追踪详情 URL 或导出接口直接访问</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 业务站点 B 审计追踪列表不展示业务站点 A 的角色管理审计记录
-2. 直接访问业务站点 A 审计详情或导出接口被拦截，不返回审计数据或 PDF 文件</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：audit_trail_coverage_rules.md、user_roles.md</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr" s="2">
+      <c r="F37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">反例</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 已登录业务站点 A 并具备审计追踪菜单权限
+2. 业务站点 B 已产生角色管理操作记录
+3. 当前用户在业务站点 B 无权限或属于不同站点</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 在业务站点 A 进入审计追踪
+2. 通过 URL 拼接或接口调用尝试访问业务站点 B 的角色管理审计记录
+3. 尝试导出业务站点 B 的角色管理审计详情</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 业务站点 A 审计追踪列表不展示业务站点 B 的角色管理审计记录
+2. 通过 URL 或接口直接访问业务站点 B 审计数据被拒绝
+3. 无法导出业务站点 B 的角色管理审计详情，不泄露跨站点数据</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md、user_roles.md</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">一般</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr" s="2">
+      <c r="M37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P35"/>
+  <autoFilter ref="A1:P37"/>
 </worksheet>
 </file>